--- a/documents/CCPRO_Directory_10312025.xlsx
+++ b/documents/CCPRO_Directory_10312025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29704"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29912"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rcc365-my.sharepoint.com/personal/jenningsl3489_rockinghamcc_edu/Documents/10. CCPRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="376" documentId="8_{2B6E75F7-0199-461C-A820-9014EF3196A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEB2FAD2-B19E-421E-A23D-28FFC37E0D72}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{65C60487-9A72-43E9-8ACE-5278B55E09DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CCPRO_Directory" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4086" uniqueCount="1003">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4106" uniqueCount="1009">
   <si>
     <t>member_name</t>
   </si>
@@ -2047,1019 +2047,1037 @@
     <t>letchworthr@nccommunitycolleges.edu</t>
   </si>
   <si>
+    <t>Rick Fasciano</t>
+  </si>
+  <si>
+    <t>Pamlico Community College</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PO Box 185 Grantsboro, NC 28529 </t>
+  </si>
+  <si>
+    <t>https://pamlicocc.edu,</t>
+  </si>
+  <si>
+    <t>252-249-1851 x3098</t>
+  </si>
+  <si>
+    <t>rfasciano@pamlicocc.edu</t>
+  </si>
+  <si>
+    <t>Carmen Kludy</t>
+  </si>
+  <si>
+    <t>Program Support Coordinator</t>
+  </si>
+  <si>
+    <t>252-249-1851 x3039</t>
+  </si>
+  <si>
+    <t>ckludy@pamlicocc.edu</t>
+  </si>
+  <si>
+    <t>Hunter Asworth</t>
+  </si>
+  <si>
+    <t>Piedmont Community College</t>
+  </si>
+  <si>
+    <t>1715 College Drive Roxboro, NC 27573</t>
+  </si>
+  <si>
+    <t>https://piedmontcc.edu/,</t>
+  </si>
+  <si>
+    <t>336-322-2110</t>
+  </si>
+  <si>
+    <t>hunter.ashworth@piedmontcc.edu</t>
+  </si>
+  <si>
+    <t>Michele Mathis</t>
+  </si>
+  <si>
+    <t>Director, Research and Institutional Effectiveness</t>
+  </si>
+  <si>
+    <t>1415 College Drive, Roxboro, NC 27573</t>
+  </si>
+  <si>
+    <t>https://www.piedmontcc.edu,</t>
+  </si>
+  <si>
+    <t>336-322-2237</t>
+  </si>
+  <si>
+    <t>Michele.Mathis@piedmontcc.edu</t>
+  </si>
+  <si>
+    <t>Dr. Nayoung Kim</t>
+  </si>
+  <si>
+    <t>Director, Institutional Research</t>
+  </si>
+  <si>
+    <t>Pitt Community College</t>
+  </si>
+  <si>
+    <t>1986 Pitt Tech Road, Greenville NC 27835</t>
+  </si>
+  <si>
+    <t>http://www.pittcc.edu/,</t>
+  </si>
+  <si>
+    <t>252-493-7296</t>
+  </si>
+  <si>
+    <t>nkim506@my.pittcc.edu</t>
+  </si>
+  <si>
+    <t>Jennifer G. Joyner</t>
+  </si>
+  <si>
+    <t>Coordinator of Survey Research</t>
+  </si>
+  <si>
+    <t>252-493-7384</t>
+  </si>
+  <si>
+    <t>jgjoyner416@my.pittcc.edu</t>
+  </si>
+  <si>
+    <t>Dr. Brian P. Miller</t>
+  </si>
+  <si>
+    <t>Vice President, Research and Technology</t>
+  </si>
+  <si>
+    <t>252-493-7421</t>
+  </si>
+  <si>
+    <t>bpmiller112@my.pittcc.edu</t>
+  </si>
+  <si>
+    <t>Dr. Brandy Leder</t>
+  </si>
+  <si>
+    <t>Senior Director for Planning and Research</t>
+  </si>
+  <si>
+    <t>252.493.3068</t>
+  </si>
+  <si>
+    <t>Bnleder571@my.pittcc.edu</t>
+  </si>
+  <si>
+    <t>Adrianne Phillips</t>
+  </si>
+  <si>
+    <t>Randolph Community College</t>
+  </si>
+  <si>
+    <t>629 Industrial Park Avenue, Asheboro, NC 27205</t>
+  </si>
+  <si>
+    <t>https://www.randolph.edu/,</t>
+  </si>
+  <si>
+    <t>336-318-0025</t>
+  </si>
+  <si>
+    <t>amphillips@randolph.edu</t>
+  </si>
+  <si>
+    <t>Stacy Schmitt</t>
+  </si>
+  <si>
+    <t>Planning and Assessment Analyst</t>
+  </si>
+  <si>
+    <t>https://www.randolph.edu,</t>
+  </si>
+  <si>
+    <t>scschmitt@randolph.edu</t>
+  </si>
+  <si>
+    <t>Shelly Greene</t>
+  </si>
+  <si>
+    <t>Associate Vice President for Institutional Advancement</t>
+  </si>
+  <si>
+    <t>336-633-0174</t>
+  </si>
+  <si>
+    <t>swgreene@randolph.edu</t>
+  </si>
+  <si>
+    <t>Heath Milligan</t>
+  </si>
+  <si>
+    <t>Accreditation and Compliance Specialist</t>
+  </si>
+  <si>
+    <t>Richmond Community College</t>
+  </si>
+  <si>
+    <t>1042 W. Hamlet Ave., PO Box 1189, Hamlet, NC 28345</t>
+  </si>
+  <si>
+    <t>https://richmondcc.edu/,</t>
+  </si>
+  <si>
+    <t>910-410-1933</t>
+  </si>
+  <si>
+    <t>jhmilligan@richmondcc.edu</t>
+  </si>
+  <si>
+    <t>Sheri Dunn-Ramsay</t>
+  </si>
+  <si>
+    <t>Associate Vice President of Marketing and Strategic Planning</t>
+  </si>
+  <si>
+    <t>1042 West Hamlet Avenue, Hamlet, NC 28345</t>
+  </si>
+  <si>
+    <t>http://richmondcc.edu,</t>
+  </si>
+  <si>
+    <t>910-410-1907</t>
+  </si>
+  <si>
+    <t>srdunn-ramsay@richmondcc.edu</t>
+  </si>
+  <si>
+    <t>Chihoko Terry</t>
+  </si>
+  <si>
+    <t>910-410-1821</t>
+  </si>
+  <si>
+    <t>ckterry@richmondcc.edu</t>
+  </si>
+  <si>
+    <t>Michael Jefferson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Associate Vice President of Academics and Institutional Effectiveness </t>
+  </si>
+  <si>
+    <t>Roanoke Chowan Community College</t>
+  </si>
+  <si>
+    <t>109 Community College Rd Ahoskie, NC 27910</t>
+  </si>
+  <si>
+    <t>https://www.roanokechowan.edu/,</t>
+  </si>
+  <si>
+    <t>(252) 862-1200 ext. 375</t>
+  </si>
+  <si>
+    <t>mjefferson7176@roanokechowan.edu</t>
+  </si>
+  <si>
+    <t>Lynn Criswell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of Institutional Assessment, Accreditation, and Special Projects </t>
+  </si>
+  <si>
+    <t>Robeson Community College</t>
+  </si>
+  <si>
+    <t>PO Box 1420, Lumberton, NC 28359</t>
+  </si>
+  <si>
+    <t>https://www.robeson.edu/,</t>
+  </si>
+  <si>
+    <t>910-272-3301</t>
+  </si>
+  <si>
+    <t>lcriswell@robeson.edu</t>
+  </si>
+  <si>
+    <t>LaRonda Lowery</t>
+  </si>
+  <si>
+    <t>AVP - Instruction and Strategic Initiatives</t>
+  </si>
+  <si>
+    <t>5160 Fayetteville Road Lumberton, NC 28360</t>
+  </si>
+  <si>
+    <t>910-272-3305</t>
+  </si>
+  <si>
+    <t>lalowery@robeson.edu</t>
+  </si>
+  <si>
+    <t>Connie Ivey</t>
+  </si>
+  <si>
+    <t>Assistant Vice President for Health Science and University Transfer</t>
+  </si>
+  <si>
+    <t>5160 Fayetteville Road, Lumberton, NC 28360</t>
+  </si>
+  <si>
+    <t>civey@robeson.edu</t>
+  </si>
+  <si>
+    <t>Josh Osborne</t>
+  </si>
+  <si>
+    <t>Director of Information Systems and Institutional Research</t>
+  </si>
+  <si>
+    <t>Rockingham Community College</t>
+  </si>
+  <si>
+    <t>PO Box 38 Wentworth, NC 27375</t>
+  </si>
+  <si>
+    <t>https://rockinghamcc.edu,</t>
+  </si>
+  <si>
+    <t>336-342-4261 x2014</t>
+  </si>
+  <si>
+    <t>osbornej3012@rockinghamcc.edu</t>
+  </si>
+  <si>
+    <t>Laura Jennings</t>
+  </si>
+  <si>
+    <t>Associate Vice President for Technology and Institutional Effectiveness</t>
+  </si>
+  <si>
+    <t>PO Box 38, Wentworth, NC 27375</t>
+  </si>
+  <si>
+    <t>http://www.rockinghamcc.edu,</t>
+  </si>
+  <si>
+    <t>(336) 342-4261</t>
+  </si>
+  <si>
+    <t>jenningsl3489@rockinghamcc.edu</t>
+  </si>
+  <si>
+    <t>Zack Hubbard</t>
+  </si>
+  <si>
+    <t>Chief Officer of Institutional Effectiveness and Information Services</t>
+  </si>
+  <si>
+    <t>Rowan-Cabarrus Community College</t>
+  </si>
+  <si>
+    <t>North Campus 1333 Jake Alexander Blvd., S. Salisbury, N.C. 28146</t>
+  </si>
+  <si>
+    <t>https://rccc.edu,</t>
+  </si>
+  <si>
+    <t>704-223-4053</t>
+  </si>
+  <si>
+    <t>zackary.hubbard@rccc.edu</t>
+  </si>
+  <si>
+    <t>Misty Santiago</t>
+  </si>
+  <si>
+    <t>Research Assistant</t>
+  </si>
+  <si>
+    <t>1333 Jake Alexander Blvd. S Salisbury, NC 28146</t>
+  </si>
+  <si>
+    <t>https://www.rccc.edu/,</t>
+  </si>
+  <si>
+    <t>704-216-7222</t>
+  </si>
+  <si>
+    <t>misty.santiago@rccc.edu</t>
+  </si>
+  <si>
+    <t>Robert Austin</t>
+  </si>
+  <si>
+    <t>Data Visualization- Institutional Effectiveness</t>
+  </si>
+  <si>
+    <t>1333 Jake Alexander Boulevard, Salisbury, NC 28146</t>
+  </si>
+  <si>
+    <t>https://www.rccc.edu,</t>
+  </si>
+  <si>
+    <t>704-216-7296</t>
+  </si>
+  <si>
+    <t>robert.austin@rccc.edu</t>
+  </si>
+  <si>
+    <t>Dr. Michael Quillen</t>
+  </si>
+  <si>
+    <t>Vice President of Academic Affairs</t>
+  </si>
+  <si>
+    <t>704-216-3475</t>
+  </si>
+  <si>
+    <t>michael.quillen@rccc.edu</t>
+  </si>
+  <si>
+    <t>Dr. Angelo Markantonakis</t>
+  </si>
+  <si>
+    <t>QEP Co-Chair/ Assistant Vice President, Academic Programs</t>
+  </si>
+  <si>
+    <t>704-216-3710</t>
+  </si>
+  <si>
+    <t>angelo.markantonakis@rccc.edu</t>
+  </si>
+  <si>
+    <t>Emily Ko</t>
+  </si>
+  <si>
+    <t>Director of Academic Services</t>
+  </si>
+  <si>
+    <t>Sampson Community College</t>
+  </si>
+  <si>
+    <t>PO Box 318, Clinton, NC 28329</t>
+  </si>
+  <si>
+    <t>http://www.sampsoncc.edu,</t>
+  </si>
+  <si>
+    <t>910-900-4137</t>
+  </si>
+  <si>
+    <t>eko@sampsoncc.edu</t>
+  </si>
+  <si>
+    <t>Dr. Marvin Rondón</t>
+  </si>
+  <si>
+    <t>Dean of Student Services and IE</t>
+  </si>
+  <si>
+    <t>1801 Sunset Ave, Clinton, North Carolina 28328</t>
+  </si>
+  <si>
+    <t>(910) 900-4076</t>
+  </si>
+  <si>
+    <t>mrondon@sampsoncc.edu</t>
+  </si>
+  <si>
+    <t>Angela Warner</t>
+  </si>
+  <si>
+    <t>Planning and Research Coordinator</t>
+  </si>
+  <si>
+    <t>1801 Sunset Avenue, Clinton, NC 28329</t>
+  </si>
+  <si>
+    <t>https://www.sampsoncc.edu/,</t>
+  </si>
+  <si>
+    <t>910-592-8081</t>
+  </si>
+  <si>
+    <t>awarner@sampsoncc.edu</t>
+  </si>
+  <si>
+    <t>Valerie Whitley</t>
+  </si>
+  <si>
+    <t>Sandhills Community College</t>
+  </si>
+  <si>
+    <t>3395 Airport Road, Pinehurst, NC 28374</t>
+  </si>
+  <si>
+    <t>http://www.sandhills.edu,</t>
+  </si>
+  <si>
+    <t>910-246-5368</t>
+  </si>
+  <si>
+    <t>whitleyv@sandhills.edu</t>
+  </si>
+  <si>
+    <t>Stephanie Miller</t>
+  </si>
+  <si>
+    <t>Research and Assessment Analyst</t>
+  </si>
+  <si>
+    <t>910-246-2859</t>
+  </si>
+  <si>
+    <t>millers@sandhills.edu</t>
+  </si>
+  <si>
+    <t>Lindsey Farmer</t>
+  </si>
+  <si>
+    <t>Dean of Workforce Innovation and Strategic Planning</t>
+  </si>
+  <si>
+    <t>910-695-3907</t>
+  </si>
+  <si>
+    <t>farmerl@sandhills.edu</t>
+  </si>
+  <si>
+    <t>Kim Sandoval</t>
+  </si>
+  <si>
+    <t>Institutional Researcher and Project Manager</t>
+  </si>
+  <si>
+    <t>South Piedmont Community College</t>
+  </si>
+  <si>
+    <t>4209 Old Charlotte Highway, Monroe, NC 28110</t>
+  </si>
+  <si>
+    <t>http://www.spcc.edu,</t>
+  </si>
+  <si>
+    <t>704-290-5873</t>
+  </si>
+  <si>
+    <t>ksandoval@spcc.edu</t>
+  </si>
+  <si>
+    <t>Jill Millard</t>
+  </si>
+  <si>
+    <t>Associate Vice President Planning and Institutional Effectiveness</t>
+  </si>
+  <si>
+    <t>704-290-5887</t>
+  </si>
+  <si>
+    <t>jmillard@spcc.edu</t>
+  </si>
+  <si>
+    <t>Christine Teach</t>
+  </si>
+  <si>
+    <t>704-290-5833</t>
+  </si>
+  <si>
+    <t>CTeach@spcc.edu</t>
+  </si>
+  <si>
+    <t>Dr. Natalie Hinson</t>
+  </si>
+  <si>
+    <t>Southeastern Community College</t>
+  </si>
+  <si>
+    <t>4564 Chadbourn Hwy, Whiteville, NC 28472</t>
+  </si>
+  <si>
+    <t>https://www.sccnc.edu/,</t>
+  </si>
+  <si>
+    <t>(910) 788-6361</t>
+  </si>
+  <si>
+    <t>natalie.hinson@sccnc.edu</t>
+  </si>
+  <si>
+    <t>Carol Ann Lydon</t>
+  </si>
+  <si>
+    <t>Associate Dean, Institutional Research</t>
+  </si>
+  <si>
+    <t>http://www.sccnc.edu,</t>
+  </si>
+  <si>
+    <t>910-788-6224</t>
+  </si>
+  <si>
+    <t>carolann.lydon@sccnc.edu</t>
+  </si>
+  <si>
+    <t>Andrea Stamper</t>
+  </si>
+  <si>
+    <t>Director of Institutional Research and Planning</t>
+  </si>
+  <si>
+    <t>Southwestern Community College</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447 College Dr., Sylva, NC 28779 </t>
+  </si>
+  <si>
+    <t>https://southwesterncc.edu/,</t>
+  </si>
+  <si>
+    <t>828-339-4614</t>
+  </si>
+  <si>
+    <t>a_stamper@southwesterncc.edu</t>
+  </si>
+  <si>
+    <t>Savvy DeHart</t>
+  </si>
+  <si>
+    <t>47 College Dr, Sylva, NC 28779</t>
+  </si>
+  <si>
+    <t>https://www.southwesterncc.edu,</t>
+  </si>
+  <si>
+    <t>828-339-4268</t>
+  </si>
+  <si>
+    <t>s_dehart@southwesterncc.edu</t>
+  </si>
+  <si>
+    <t>Wanda Knight</t>
+  </si>
+  <si>
+    <t>Institutional Research and Planning Associate</t>
+  </si>
+  <si>
+    <t>447 College Drive, Sylva, NCÿ28779</t>
+  </si>
+  <si>
+    <t>https://www.southwesterncc.edu/,</t>
+  </si>
+  <si>
+    <t>828-339-4236</t>
+  </si>
+  <si>
+    <t>w_knight@southwesterncc.edu</t>
+  </si>
+  <si>
+    <t>Dr. Cindy Dean</t>
+  </si>
+  <si>
+    <t>Stanly  Community College</t>
+  </si>
+  <si>
+    <t>141 College Drive, Albemarle, NC 28001</t>
+  </si>
+  <si>
+    <t>https://www.stanly.edu,</t>
+  </si>
+  <si>
+    <t>704-991-0329</t>
+  </si>
+  <si>
+    <t>cdean5600@stanly.edu</t>
+  </si>
+  <si>
+    <t>Katrina Sams</t>
+  </si>
+  <si>
+    <t>Institutional Effectiveness Assistant</t>
+  </si>
+  <si>
+    <t>Stanly Community College</t>
+  </si>
+  <si>
+    <t>704-991-0179</t>
+  </si>
+  <si>
+    <t>ksams1619@stanly.edu</t>
+  </si>
+  <si>
+    <t>Pamela Marion</t>
+  </si>
+  <si>
+    <t>Senior Analytics Specialist</t>
+  </si>
+  <si>
+    <t>Surry Community College</t>
+  </si>
+  <si>
+    <t>630 S Main St, Dobson, NC 27017</t>
+  </si>
+  <si>
+    <t>https://surry.edu/,</t>
+  </si>
+  <si>
+    <t>336-386-3513</t>
+  </si>
+  <si>
+    <t>marionpj@surry.edu</t>
+  </si>
+  <si>
+    <t>Dr. Katie D Bowman</t>
+  </si>
+  <si>
+    <t>(336) 386-3635</t>
+  </si>
+  <si>
+    <t>bowmankd@surry.edu</t>
+  </si>
+  <si>
+    <t>Robin Slate</t>
+  </si>
+  <si>
+    <t>Data Technician</t>
+  </si>
+  <si>
+    <t>630 South Main Street, Dobson, NC 27017</t>
+  </si>
+  <si>
+    <t>https://www.surry.edu,</t>
+  </si>
+  <si>
+    <t>336-386-3451</t>
+  </si>
+  <si>
+    <t>slater@surry.edu</t>
+  </si>
+  <si>
+    <t>Michael Faulkner</t>
+  </si>
+  <si>
+    <t>Executive Director of Institutional Research</t>
+  </si>
+  <si>
+    <t>336-386-3436</t>
+  </si>
+  <si>
+    <t>faulknerm@surry.edu</t>
+  </si>
+  <si>
+    <t>Stephen Wood</t>
+  </si>
+  <si>
+    <t>Vice President for Instruction and Institutional Effectiveness</t>
+  </si>
+  <si>
+    <t>Tri-County Community College</t>
+  </si>
+  <si>
+    <t>21 Campus Circle, Murphy, NC 28906</t>
+  </si>
+  <si>
+    <t>http://www.tricountycc.edu/,</t>
+  </si>
+  <si>
+    <t>828-835-4254</t>
+  </si>
+  <si>
+    <t>swood@tricountycc.edu</t>
+  </si>
+  <si>
+    <t>Jason Chambers</t>
+  </si>
+  <si>
+    <t>Dean of Research and Planning/Early College Liaison</t>
+  </si>
+  <si>
+    <t>828-835-4297</t>
+  </si>
+  <si>
+    <t>jchambers@tricountycc.edu</t>
+  </si>
+  <si>
+    <t>Julie Hicks</t>
+  </si>
+  <si>
+    <t>Director of Planning and Research</t>
+  </si>
+  <si>
+    <t>Vance-Granville Community College</t>
+  </si>
+  <si>
+    <t>200 Community College Road, Henderson, NC 27536</t>
+  </si>
+  <si>
+    <t>https://www.vgcc.edu,</t>
+  </si>
+  <si>
+    <t>252-738-3250</t>
+  </si>
+  <si>
+    <t>hicksj@vgcc.edu</t>
+  </si>
+  <si>
+    <t>Andrea McDaniel</t>
+  </si>
+  <si>
+    <t>252-738-3413</t>
+  </si>
+  <si>
+    <t>mcdaniela@vgcc.edu</t>
+  </si>
+  <si>
+    <t>Dafney Jones</t>
+  </si>
+  <si>
+    <t>Institutional Research Coordinator</t>
+  </si>
+  <si>
+    <t>jonesd@vgcc.edu</t>
+  </si>
+  <si>
+    <t>John Richard Smith</t>
+  </si>
+  <si>
+    <t>Wake Technical Community College</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9101 Fayetteville Rd Raleigh, NC 27603 </t>
+  </si>
+  <si>
+    <t>https://www.waketech.edu/,</t>
+  </si>
+  <si>
+    <t>252-241-4079</t>
+  </si>
+  <si>
+    <t>jrsmith29@waketech.edu</t>
+  </si>
+  <si>
+    <t>John Robert Bakken</t>
+  </si>
+  <si>
+    <t>Dean of Curriculum Support - Curriculum Education Services (CCPRO Associate Member)</t>
+  </si>
+  <si>
+    <t>9101 Fayetteville Road, Raleigh, NC 27603</t>
+  </si>
+  <si>
+    <t>https://www.waketech.edu,</t>
+  </si>
+  <si>
+    <t>919-866-5319</t>
+  </si>
+  <si>
+    <t>jrbakken@waketech.edu</t>
+  </si>
+  <si>
+    <t>Dr. Rachel Madsen</t>
+  </si>
+  <si>
+    <t>919-866-5514</t>
+  </si>
+  <si>
+    <t>rsmadsen@waketech.edu</t>
+  </si>
+  <si>
+    <t>Carrie E. Bartek</t>
+  </si>
+  <si>
+    <t>Dean of College Iniatives and Assessment</t>
+  </si>
+  <si>
+    <t>919-866-5586</t>
+  </si>
+  <si>
+    <t>cebartek@waketech.edu</t>
+  </si>
+  <si>
+    <t>Anna Jones</t>
+  </si>
+  <si>
+    <t>Director of Accreditation and Compliance</t>
+  </si>
+  <si>
+    <t>919-866-5232</t>
+  </si>
+  <si>
+    <t>aejones13@waketech.edu</t>
+  </si>
+  <si>
+    <t>Dr. Patricia Pfeiffer</t>
+  </si>
+  <si>
+    <t>President</t>
+  </si>
+  <si>
+    <t>Wayne Community College</t>
+  </si>
+  <si>
+    <t>3000 Wayne Memorial Drive, Goldsboro, NC 27534</t>
+  </si>
+  <si>
+    <t>https://www.waynecc.edu/,</t>
+  </si>
+  <si>
+    <t>919-739-7000</t>
+  </si>
+  <si>
+    <t>pfeiffer@waynecc.edu</t>
+  </si>
+  <si>
+    <t>Dr. Dorothy Moore</t>
+  </si>
+  <si>
+    <t>Associate Vice President of Institutional Effectiveness and  Chief of Staff</t>
+  </si>
+  <si>
+    <t>919-739-7010</t>
+  </si>
+  <si>
+    <t>dpmoore@waynecc.edu</t>
+  </si>
+  <si>
+    <t>Becky Mulligan</t>
+  </si>
+  <si>
+    <t>Institutional Effectiveness Coordinator</t>
+  </si>
+  <si>
+    <t>919-739-7009</t>
+  </si>
+  <si>
+    <t>bmull1@waynecc.edu</t>
+  </si>
+  <si>
+    <t>Katie Dunnagan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordinator, Institutional Research and Evaluation </t>
+  </si>
+  <si>
+    <t>Western Piedmont Community College</t>
+  </si>
+  <si>
+    <t>1001 Burkemont Avenue, Morganton, NC 28655</t>
+  </si>
+  <si>
+    <t>http://www.wpcc.edu/,</t>
+  </si>
+  <si>
+    <t>828-448-3171</t>
+  </si>
+  <si>
+    <t>kdunnagan@wpcc.edu</t>
+  </si>
+  <si>
+    <t>Susan Berley</t>
+  </si>
+  <si>
+    <t>Director of Institutional Research and Evaluation</t>
+  </si>
+  <si>
+    <t>828-448-6125</t>
+  </si>
+  <si>
+    <t>sberley@wpcc.edu</t>
+  </si>
+  <si>
+    <t>Jody Call</t>
+  </si>
+  <si>
+    <t>Executive Director - Institutional Research and Planning</t>
+  </si>
+  <si>
+    <t>Wilkes Community College</t>
+  </si>
+  <si>
+    <t>1328 S Collegiate Drive Wilkesboro, NC 28697</t>
+  </si>
+  <si>
+    <t>336-838-6233</t>
+  </si>
+  <si>
+    <t>jrcall337@wilkescc.edu</t>
+  </si>
+  <si>
+    <t>Adam Parsons</t>
+  </si>
+  <si>
+    <t>1328 South Collegiate Drive, Wilkesboro, NC 28697</t>
+  </si>
+  <si>
+    <t>https://www.wilkescc.edu/,</t>
+  </si>
+  <si>
+    <t>336-838-6258</t>
+  </si>
+  <si>
+    <t>acparsons220@wilkescc.edu</t>
+  </si>
+  <si>
+    <t>Brittany Wallace</t>
+  </si>
+  <si>
+    <t>Wilson Community College</t>
+  </si>
+  <si>
+    <t>P.O. Box 4305, 902 Herring Avenue, Wilson, NC 27893</t>
+  </si>
+  <si>
+    <t>https://www.wilsoncc.edu,</t>
+  </si>
+  <si>
+    <t>252-246-1311</t>
+  </si>
+  <si>
+    <t>bwallace@wilsoncc.edu</t>
+  </si>
+  <si>
+    <t>rose.webster@alamancecc.edu</t>
+  </si>
+  <si>
+    <t>Dean of Planning and Research</t>
+  </si>
+  <si>
+    <t>Financial Aid Coordinator/Student Retention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">800 College Rd New Bern, NC 28560 </t>
+  </si>
+  <si>
+    <t>(252) 638-7349</t>
+  </si>
+  <si>
+    <t>Dr. Anna Jones</t>
+  </si>
+  <si>
+    <t>Assistant Vice President, Planning and Research</t>
+  </si>
+  <si>
+    <t>252-493-7530</t>
+  </si>
+  <si>
+    <t>aejones870@my.pittcc.edu</t>
+  </si>
+  <si>
+    <t>ermiller781@alamancecc.edu</t>
+  </si>
+  <si>
     <t>Brandy Leder</t>
   </si>
   <si>
-    <t>Pamlico Community College</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO Box 185 Grantsboro, NC 28529 </t>
-  </si>
-  <si>
-    <t>https://pamlicocc.edu,</t>
-  </si>
-  <si>
-    <t>252-249-1851 x3064</t>
-  </si>
-  <si>
     <t>bleder@pamlicocc.edu</t>
-  </si>
-  <si>
-    <t>Carmen Kludy</t>
-  </si>
-  <si>
-    <t>Program Support Coordinator</t>
-  </si>
-  <si>
-    <t>252-249-1851 x3039</t>
-  </si>
-  <si>
-    <t>ckludy@pamlicocc.edu</t>
-  </si>
-  <si>
-    <t>Hunter Asworth</t>
-  </si>
-  <si>
-    <t>Piedmont Community College</t>
-  </si>
-  <si>
-    <t>1715 College Drive Roxboro, NC 27573</t>
-  </si>
-  <si>
-    <t>https://piedmontcc.edu/,</t>
-  </si>
-  <si>
-    <t>336-322-2110</t>
-  </si>
-  <si>
-    <t>hunter.ashworth@piedmontcc.edu</t>
-  </si>
-  <si>
-    <t>Michele Mathis</t>
-  </si>
-  <si>
-    <t>Director, Research and Institutional Effectiveness</t>
-  </si>
-  <si>
-    <t>1415 College Drive, Roxboro, NC 27573</t>
-  </si>
-  <si>
-    <t>https://www.piedmontcc.edu,</t>
-  </si>
-  <si>
-    <t>336-322-2237</t>
-  </si>
-  <si>
-    <t>Michele.Mathis@piedmontcc.edu</t>
-  </si>
-  <si>
-    <t>Dr. Nayoung Kim</t>
-  </si>
-  <si>
-    <t>Director, Institutional Research</t>
-  </si>
-  <si>
-    <t>Pitt Community College</t>
-  </si>
-  <si>
-    <t>1986 Pitt Tech Road, Greenville NC 27835</t>
-  </si>
-  <si>
-    <t>http://www.pittcc.edu/,</t>
-  </si>
-  <si>
-    <t>252-493-7296</t>
-  </si>
-  <si>
-    <t>nkim506@my.pittcc.edu</t>
-  </si>
-  <si>
-    <t>Jennifer G. Joyner</t>
-  </si>
-  <si>
-    <t>Coordinator of Survey Research</t>
-  </si>
-  <si>
-    <t>252-493-7384</t>
-  </si>
-  <si>
-    <t>jgjoyner416@my.pittcc.edu</t>
-  </si>
-  <si>
-    <t>Dr. Brian P. Miller</t>
-  </si>
-  <si>
-    <t>Vice President, Research and Technology</t>
-  </si>
-  <si>
-    <t>252-493-7421</t>
-  </si>
-  <si>
-    <t>bpmiller112@my.pittcc.edu</t>
-  </si>
-  <si>
-    <t>Adrianne Phillips</t>
-  </si>
-  <si>
-    <t>Randolph Community College</t>
-  </si>
-  <si>
-    <t>629 Industrial Park Avenue, Asheboro, NC 27205</t>
-  </si>
-  <si>
-    <t>https://www.randolph.edu/,</t>
-  </si>
-  <si>
-    <t>336-318-0025</t>
-  </si>
-  <si>
-    <t>amphillips@randolph.edu</t>
-  </si>
-  <si>
-    <t>Stacy Schmitt</t>
-  </si>
-  <si>
-    <t>Planning and Assessment Analyst</t>
-  </si>
-  <si>
-    <t>https://www.randolph.edu,</t>
-  </si>
-  <si>
-    <t>scschmitt@randolph.edu</t>
-  </si>
-  <si>
-    <t>Shelly Greene</t>
-  </si>
-  <si>
-    <t>Associate Vice President for Institutional Advancement</t>
-  </si>
-  <si>
-    <t>336-633-0174</t>
-  </si>
-  <si>
-    <t>swgreene@randolph.edu</t>
-  </si>
-  <si>
-    <t>Heath Milligan</t>
-  </si>
-  <si>
-    <t>Accreditation and Compliance Specialist</t>
-  </si>
-  <si>
-    <t>Richmond Community College</t>
-  </si>
-  <si>
-    <t>1042 W. Hamlet Ave., PO Box 1189, Hamlet, NC 28345</t>
-  </si>
-  <si>
-    <t>https://richmondcc.edu/,</t>
-  </si>
-  <si>
-    <t>910-410-1933</t>
-  </si>
-  <si>
-    <t>jhmilligan@richmondcc.edu</t>
-  </si>
-  <si>
-    <t>Sheri Dunn-Ramsay</t>
-  </si>
-  <si>
-    <t>Associate Vice President of Marketing and Strategic Planning</t>
-  </si>
-  <si>
-    <t>1042 West Hamlet Avenue, Hamlet, NC 28345</t>
-  </si>
-  <si>
-    <t>http://richmondcc.edu,</t>
-  </si>
-  <si>
-    <t>910-410-1907</t>
-  </si>
-  <si>
-    <t>srdunn-ramsay@richmondcc.edu</t>
-  </si>
-  <si>
-    <t>Chihoko Terry</t>
-  </si>
-  <si>
-    <t>910-410-1821</t>
-  </si>
-  <si>
-    <t>ckterry@richmondcc.edu</t>
-  </si>
-  <si>
-    <t>Michael Jefferson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Associate Vice President of Academics and Institutional Effectiveness </t>
-  </si>
-  <si>
-    <t>Roanoke Chowan Community College</t>
-  </si>
-  <si>
-    <t>109 Community College Rd Ahoskie, NC 27910</t>
-  </si>
-  <si>
-    <t>https://www.roanokechowan.edu/,</t>
-  </si>
-  <si>
-    <t>(252) 862-1200 ext. 375</t>
-  </si>
-  <si>
-    <t>mjefferson7176@roanokechowan.edu</t>
-  </si>
-  <si>
-    <t>Lynn Criswell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of Institutional Assessment, Accreditation, and Special Projects </t>
-  </si>
-  <si>
-    <t>Robeson Community College</t>
-  </si>
-  <si>
-    <t>PO Box 1420, Lumberton, NC 28359</t>
-  </si>
-  <si>
-    <t>https://www.robeson.edu/,</t>
-  </si>
-  <si>
-    <t>910-272-3301</t>
-  </si>
-  <si>
-    <t>lcriswell@robeson.edu</t>
-  </si>
-  <si>
-    <t>LaRonda Lowery</t>
-  </si>
-  <si>
-    <t>AVP - Instruction and Strategic Initiatives</t>
-  </si>
-  <si>
-    <t>5160 Fayetteville Road Lumberton, NC 28360</t>
-  </si>
-  <si>
-    <t>910-272-3305</t>
-  </si>
-  <si>
-    <t>lalowery@robeson.edu</t>
-  </si>
-  <si>
-    <t>Dr. Melissa Oxendine</t>
-  </si>
-  <si>
-    <t>Dean, Distance Education and Learning Support Services</t>
-  </si>
-  <si>
-    <t>5160 Fayetteville Road, Lumberton, NC 28360</t>
-  </si>
-  <si>
-    <t>910-272-3441</t>
-  </si>
-  <si>
-    <t>moxendine@robeson.edu</t>
-  </si>
-  <si>
-    <t>Connie Ivey</t>
-  </si>
-  <si>
-    <t>Assistant Vice President for Health Science and University Transfer</t>
-  </si>
-  <si>
-    <t>civey@robeson.edu</t>
-  </si>
-  <si>
-    <t>Josh Osborne</t>
-  </si>
-  <si>
-    <t>Systems Administrator</t>
-  </si>
-  <si>
-    <t>Rockingham Community College</t>
-  </si>
-  <si>
-    <t>PO Box 38 Wentworth, NC 27375</t>
-  </si>
-  <si>
-    <t>https://rockinghamcc.edu,</t>
-  </si>
-  <si>
-    <t>336-342-4261 x2014</t>
-  </si>
-  <si>
-    <t>osbornej3012@rockinghamcc.edu</t>
-  </si>
-  <si>
-    <t>Laura Jennings</t>
-  </si>
-  <si>
-    <t>Associate Vice President for Technology and Institutional Effectiveness</t>
-  </si>
-  <si>
-    <t>PO Box 38, Wentworth, NC 27375</t>
-  </si>
-  <si>
-    <t>http://www.rockinghamcc.edu,</t>
-  </si>
-  <si>
-    <t>(336) 342-4261</t>
-  </si>
-  <si>
-    <t>jenningsl3489@rockinghamcc.edu</t>
-  </si>
-  <si>
-    <t>Zack Hubbard</t>
-  </si>
-  <si>
-    <t>Chief Officer of Institutional Effectiveness and Information Services</t>
-  </si>
-  <si>
-    <t>Rowan-Cabarrus Community College</t>
-  </si>
-  <si>
-    <t>North Campus 1333 Jake Alexander Blvd., S. Salisbury, N.C. 28146</t>
-  </si>
-  <si>
-    <t>https://rccc.edu,</t>
-  </si>
-  <si>
-    <t>704-223-4053</t>
-  </si>
-  <si>
-    <t>zackary.hubbard@rccc.edu</t>
-  </si>
-  <si>
-    <t>Misty Santiago</t>
-  </si>
-  <si>
-    <t>Research Assistant</t>
-  </si>
-  <si>
-    <t>1333 Jake Alexander Blvd. S Salisbury, NC 28146</t>
-  </si>
-  <si>
-    <t>https://www.rccc.edu/,</t>
-  </si>
-  <si>
-    <t>704-216-7222</t>
-  </si>
-  <si>
-    <t>misty.santiago@rccc.edu</t>
-  </si>
-  <si>
-    <t>Robert Austin</t>
-  </si>
-  <si>
-    <t>Data Visualization- Institutional Effectiveness</t>
-  </si>
-  <si>
-    <t>1333 Jake Alexander Boulevard, Salisbury, NC 28146</t>
-  </si>
-  <si>
-    <t>https://www.rccc.edu,</t>
-  </si>
-  <si>
-    <t>704-216-7296</t>
-  </si>
-  <si>
-    <t>robert.austin@rccc.edu</t>
-  </si>
-  <si>
-    <t>Dr. Michael Quillen</t>
-  </si>
-  <si>
-    <t>Vice President of Academic Affairs</t>
-  </si>
-  <si>
-    <t>704-216-3475</t>
-  </si>
-  <si>
-    <t>michael.quillen@rccc.edu</t>
-  </si>
-  <si>
-    <t>Dr. Angelo Markantonakis</t>
-  </si>
-  <si>
-    <t>QEP Co-Chair/ Assistant Vice President, Academic Programs</t>
-  </si>
-  <si>
-    <t>704-216-3710</t>
-  </si>
-  <si>
-    <t>angelo.markantonakis@rccc.edu</t>
-  </si>
-  <si>
-    <t>Emily Ko</t>
-  </si>
-  <si>
-    <t>Director of Academic Services</t>
-  </si>
-  <si>
-    <t>Sampson Community College</t>
-  </si>
-  <si>
-    <t>PO Box 318, Clinton, NC 28329</t>
-  </si>
-  <si>
-    <t>http://www.sampsoncc.edu,</t>
-  </si>
-  <si>
-    <t>910-900-4137</t>
-  </si>
-  <si>
-    <t>eko@sampsoncc.edu</t>
-  </si>
-  <si>
-    <t>Dr. Marvin Rondón</t>
-  </si>
-  <si>
-    <t>Dean of Student Services and IE</t>
-  </si>
-  <si>
-    <t>1801 Sunset Ave, Clinton, North Carolina 28328</t>
-  </si>
-  <si>
-    <t>(910) 900-4076</t>
-  </si>
-  <si>
-    <t>mrondon@sampsoncc.edu</t>
-  </si>
-  <si>
-    <t>Angela Warner</t>
-  </si>
-  <si>
-    <t>Planning and Research Coordinator</t>
-  </si>
-  <si>
-    <t>1801 Sunset Avenue, Clinton, NC 28329</t>
-  </si>
-  <si>
-    <t>https://www.sampsoncc.edu/,</t>
-  </si>
-  <si>
-    <t>910-592-8081</t>
-  </si>
-  <si>
-    <t>awarner@sampsoncc.edu</t>
-  </si>
-  <si>
-    <t>Stephanie Miller</t>
-  </si>
-  <si>
-    <t>Research and Assessment Analyst</t>
-  </si>
-  <si>
-    <t>Sandhills Community College</t>
-  </si>
-  <si>
-    <t>3395 Airport Road, Pinehurst, NC 28374</t>
-  </si>
-  <si>
-    <t>http://www.sandhills.edu,</t>
-  </si>
-  <si>
-    <t>910-246-2859</t>
-  </si>
-  <si>
-    <t>millers@sandhills.edu</t>
-  </si>
-  <si>
-    <t>Lindsey Farmer</t>
-  </si>
-  <si>
-    <t>Dean of Planning and Research</t>
-  </si>
-  <si>
-    <t>910-695-3907</t>
-  </si>
-  <si>
-    <t>farmerl@sandhills.edu</t>
-  </si>
-  <si>
-    <t>Kim Sandoval</t>
-  </si>
-  <si>
-    <t>Institutional Researcher and Project Manager</t>
-  </si>
-  <si>
-    <t>South Piedmont Community College</t>
-  </si>
-  <si>
-    <t>4209 Old Charlotte Highway, Monroe, NC 28110</t>
-  </si>
-  <si>
-    <t>http://www.spcc.edu,</t>
-  </si>
-  <si>
-    <t>704-290-5873</t>
-  </si>
-  <si>
-    <t>ksandoval@spcc.edu</t>
-  </si>
-  <si>
-    <t>Jill Millard</t>
-  </si>
-  <si>
-    <t>Associate Vice President Planning and Institutional Effectiveness</t>
-  </si>
-  <si>
-    <t>704-290-5887</t>
-  </si>
-  <si>
-    <t>jmillard@spcc.edu</t>
-  </si>
-  <si>
-    <t>Christine Teach</t>
-  </si>
-  <si>
-    <t>704-290-5833</t>
-  </si>
-  <si>
-    <t>CTeach@spcc.edu</t>
-  </si>
-  <si>
-    <t>Dr. Natalie Hinson</t>
-  </si>
-  <si>
-    <t>Southeastern Community College</t>
-  </si>
-  <si>
-    <t>4564 Chadbourn Hwy, Whiteville, NC 28472</t>
-  </si>
-  <si>
-    <t>https://www.sccnc.edu/,</t>
-  </si>
-  <si>
-    <t>(910) 788-6361</t>
-  </si>
-  <si>
-    <t>natalie.hinson@sccnc.edu</t>
-  </si>
-  <si>
-    <t>Carol Ann Lydon</t>
-  </si>
-  <si>
-    <t>Associate Dean, Institutional Research</t>
-  </si>
-  <si>
-    <t>http://www.sccnc.edu,</t>
-  </si>
-  <si>
-    <t>910-788-6224</t>
-  </si>
-  <si>
-    <t>carolann.lydon@sccnc.edu</t>
-  </si>
-  <si>
-    <t>Andrea Stamper</t>
-  </si>
-  <si>
-    <t>Director of Institutional Research and Planning</t>
-  </si>
-  <si>
-    <t>Southwestern Community College</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447 College Dr., Sylva, NC 28779 </t>
-  </si>
-  <si>
-    <t>https://southwesterncc.edu/,</t>
-  </si>
-  <si>
-    <t>828-339-4614</t>
-  </si>
-  <si>
-    <t>a_stamper@southwesterncc.edu</t>
-  </si>
-  <si>
-    <t>Savvy DeHart</t>
-  </si>
-  <si>
-    <t>47 College Dr, Sylva, NC 28779</t>
-  </si>
-  <si>
-    <t>https://www.southwesterncc.edu,</t>
-  </si>
-  <si>
-    <t>828-339-4268</t>
-  </si>
-  <si>
-    <t>s_dehart@southwesterncc.edu</t>
-  </si>
-  <si>
-    <t>Wanda Knight</t>
-  </si>
-  <si>
-    <t>Institutional Research and Planning Associate</t>
-  </si>
-  <si>
-    <t>447 College Drive, Sylva, NCÿ28779</t>
-  </si>
-  <si>
-    <t>https://www.southwesterncc.edu/,</t>
-  </si>
-  <si>
-    <t>828-339-4236</t>
-  </si>
-  <si>
-    <t>w_knight@southwesterncc.edu</t>
-  </si>
-  <si>
-    <t>Dr. Cindy Dean</t>
-  </si>
-  <si>
-    <t>Stanly  Community College</t>
-  </si>
-  <si>
-    <t>141 College Drive, Albemarle, NC 28001</t>
-  </si>
-  <si>
-    <t>https://www.stanly.edu,</t>
-  </si>
-  <si>
-    <t>704-991-0329</t>
-  </si>
-  <si>
-    <t>cdean5600@stanly.edu</t>
-  </si>
-  <si>
-    <t>Katrina Sams</t>
-  </si>
-  <si>
-    <t>Institutional Effectiveness Assistant</t>
-  </si>
-  <si>
-    <t>Stanly Community College</t>
-  </si>
-  <si>
-    <t>704-991-0179</t>
-  </si>
-  <si>
-    <t>ksams1619@stanly.edu</t>
-  </si>
-  <si>
-    <t>Pamela Marion</t>
-  </si>
-  <si>
-    <t>Senior Analytics Specialist</t>
-  </si>
-  <si>
-    <t>Surry Community College</t>
-  </si>
-  <si>
-    <t>630 S Main St, Dobson, NC 27017</t>
-  </si>
-  <si>
-    <t>https://surry.edu/,</t>
-  </si>
-  <si>
-    <t>336-386-3513</t>
-  </si>
-  <si>
-    <t>marionpj@surry.edu</t>
-  </si>
-  <si>
-    <t>Dr. Katie D Bowman</t>
-  </si>
-  <si>
-    <t>(336) 386-3635</t>
-  </si>
-  <si>
-    <t>bowmankd@surry.edu</t>
-  </si>
-  <si>
-    <t>Robin Slate</t>
-  </si>
-  <si>
-    <t>Data Technician</t>
-  </si>
-  <si>
-    <t>630 South Main Street, Dobson, NC 27017</t>
-  </si>
-  <si>
-    <t>https://www.surry.edu,</t>
-  </si>
-  <si>
-    <t>336-386-3451</t>
-  </si>
-  <si>
-    <t>slater@surry.edu</t>
-  </si>
-  <si>
-    <t>Michael Faulkner</t>
-  </si>
-  <si>
-    <t>Executive Director of Institutional Research</t>
-  </si>
-  <si>
-    <t>336-386-3436</t>
-  </si>
-  <si>
-    <t>faulknerm@surry.edu</t>
-  </si>
-  <si>
-    <t>Stephen Wood</t>
-  </si>
-  <si>
-    <t>Vice President for Instruction and Institutional Effectiveness</t>
-  </si>
-  <si>
-    <t>Tri-County Community College</t>
-  </si>
-  <si>
-    <t>21 Campus Circle, Murphy, NC 28906</t>
-  </si>
-  <si>
-    <t>http://www.tricountycc.edu/,</t>
-  </si>
-  <si>
-    <t>828-835-4254</t>
-  </si>
-  <si>
-    <t>swood@tricountycc.edu</t>
-  </si>
-  <si>
-    <t>Jason Chambers</t>
-  </si>
-  <si>
-    <t>Dean of Research and Planning/Early College Liaison</t>
-  </si>
-  <si>
-    <t>828-835-4297</t>
-  </si>
-  <si>
-    <t>jchambers@tricountycc.edu</t>
-  </si>
-  <si>
-    <t>Julie Hicks</t>
-  </si>
-  <si>
-    <t>Director of Planning and Research</t>
-  </si>
-  <si>
-    <t>Vance-Granville Community College</t>
-  </si>
-  <si>
-    <t>200 Community College Road, Henderson, NC 27536</t>
-  </si>
-  <si>
-    <t>https://www.vgcc.edu,</t>
-  </si>
-  <si>
-    <t>252-738-3250</t>
-  </si>
-  <si>
-    <t>hicksj@vgcc.edu</t>
-  </si>
-  <si>
-    <t>Andrea McDaniel</t>
-  </si>
-  <si>
-    <t>252-738-3413</t>
-  </si>
-  <si>
-    <t>mcdaniela@vgcc.edu</t>
-  </si>
-  <si>
-    <t>Dafney Jones</t>
-  </si>
-  <si>
-    <t>Institutional Research Coordinator</t>
-  </si>
-  <si>
-    <t>jonesd@vgcc.edu</t>
-  </si>
-  <si>
-    <t>John Richard Smith</t>
-  </si>
-  <si>
-    <t>Wake Technical Community College</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9101 Fayetteville Rd Raleigh, NC 27603 </t>
-  </si>
-  <si>
-    <t>https://www.waketech.edu/,</t>
-  </si>
-  <si>
-    <t>252-241-4079</t>
-  </si>
-  <si>
-    <t>jrsmith29@waketech.edu</t>
-  </si>
-  <si>
-    <t>John Robert Bakken</t>
-  </si>
-  <si>
-    <t>Dean of Curriculum Support - Curriculum Education Services (CCPRO Associate Member)</t>
-  </si>
-  <si>
-    <t>9101 Fayetteville Road, Raleigh, NC 27603</t>
-  </si>
-  <si>
-    <t>https://www.waketech.edu,</t>
-  </si>
-  <si>
-    <t>919-866-5319</t>
-  </si>
-  <si>
-    <t>jrbakken@waketech.edu</t>
-  </si>
-  <si>
-    <t>Dr. Rachel Madsen</t>
-  </si>
-  <si>
-    <t>919-866-5514</t>
-  </si>
-  <si>
-    <t>rsmadsen@waketech.edu</t>
-  </si>
-  <si>
-    <t>Carrie E. Bartek</t>
-  </si>
-  <si>
-    <t>Dean of College Iniatives and Assessment</t>
-  </si>
-  <si>
-    <t>919-866-5586</t>
-  </si>
-  <si>
-    <t>cebartek@waketech.edu</t>
-  </si>
-  <si>
-    <t>Anna Jones</t>
-  </si>
-  <si>
-    <t>Director of Accreditation and Compliance</t>
-  </si>
-  <si>
-    <t>919-866-5232</t>
-  </si>
-  <si>
-    <t>aejones13@waketech.edu</t>
-  </si>
-  <si>
-    <t>Dr. Patricia Pfeiffer</t>
-  </si>
-  <si>
-    <t>President</t>
-  </si>
-  <si>
-    <t>Wayne Community College</t>
-  </si>
-  <si>
-    <t>3000 Wayne Memorial Drive, Goldsboro, NC 27534</t>
-  </si>
-  <si>
-    <t>https://www.waynecc.edu/,</t>
-  </si>
-  <si>
-    <t>919-739-7000</t>
-  </si>
-  <si>
-    <t>pfeiffer@waynecc.edu</t>
-  </si>
-  <si>
-    <t>Dr. Dorothy Moore</t>
-  </si>
-  <si>
-    <t>Associate Vice President of Institutional Effectiveness and  Chief of Staff</t>
-  </si>
-  <si>
-    <t>919-739-7010</t>
-  </si>
-  <si>
-    <t>dpmoore@waynecc.edu</t>
-  </si>
-  <si>
-    <t>Becky Mulligan</t>
-  </si>
-  <si>
-    <t>Institutional Effectiveness Coordinator</t>
-  </si>
-  <si>
-    <t>919-739-7009</t>
-  </si>
-  <si>
-    <t>bmull1@waynecc.edu</t>
-  </si>
-  <si>
-    <t>Katie Dunnagan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coordinator, Institutional Research and Evaluation </t>
-  </si>
-  <si>
-    <t>Western Piedmont Community College</t>
-  </si>
-  <si>
-    <t>1001 Burkemont Avenue, Morganton, NC 28655</t>
-  </si>
-  <si>
-    <t>http://www.wpcc.edu/,</t>
-  </si>
-  <si>
-    <t>828-448-3171</t>
-  </si>
-  <si>
-    <t>kdunnagan@wpcc.edu</t>
-  </si>
-  <si>
-    <t>Susan Berley</t>
-  </si>
-  <si>
-    <t>Director of Institutional Research and Evaluation</t>
-  </si>
-  <si>
-    <t>828-448-6125</t>
-  </si>
-  <si>
-    <t>sberley@wpcc.edu</t>
-  </si>
-  <si>
-    <t>Jody Call</t>
-  </si>
-  <si>
-    <t>Executive Director - Institutional Research and Planning</t>
-  </si>
-  <si>
-    <t>Wilkes Community College</t>
-  </si>
-  <si>
-    <t>1328 S Collegiate Drive Wilkesboro, NC 28697</t>
-  </si>
-  <si>
-    <t>336-838-6233</t>
-  </si>
-  <si>
-    <t>jrcall337@wilkescc.edu</t>
-  </si>
-  <si>
-    <t>Adam Parsons</t>
-  </si>
-  <si>
-    <t>1328 South Collegiate Drive, Wilkesboro, NC 28697</t>
-  </si>
-  <si>
-    <t>https://www.wilkescc.edu/,</t>
-  </si>
-  <si>
-    <t>336-838-6258</t>
-  </si>
-  <si>
-    <t>acparsons220@wilkescc.edu</t>
-  </si>
-  <si>
-    <t>Brittany Wallace</t>
-  </si>
-  <si>
-    <t>Wilson Community College</t>
-  </si>
-  <si>
-    <t>P.O. Box 4305, 902 Herring Avenue, Wilson, NC 27893</t>
-  </si>
-  <si>
-    <t>https://www.wilsoncc.edu,</t>
-  </si>
-  <si>
-    <t>252-246-1311</t>
-  </si>
-  <si>
-    <t>bwallace@wilsoncc.edu</t>
-  </si>
-  <si>
-    <t>rose.webster@alamancecc.edu</t>
-  </si>
-  <si>
-    <t>Financial Aid Coordinator/Student Retention</t>
-  </si>
-  <si>
-    <t xml:space="preserve">800 College Rd New Bern, NC 28560 </t>
-  </si>
-  <si>
-    <t>(252) 638-7349</t>
-  </si>
-  <si>
-    <t>Dr. Anna Jones</t>
-  </si>
-  <si>
-    <t>Assistant Vice President, Planning and Research</t>
-  </si>
-  <si>
-    <t>252-493-7530</t>
-  </si>
-  <si>
-    <t>aejones870@my.pittcc.edu</t>
-  </si>
-  <si>
-    <t>ermiller781@alamancecc.edu</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3193,6 +3211,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="33">
@@ -3542,7 +3567,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3898,7 +3923,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J185"/>
+  <dimension ref="A1:J186"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
@@ -5631,7 +5656,7 @@
       <c r="G54" t="s">
         <v>302</v>
       </c>
-      <c r="H54" s="3" t="s">
+      <c r="H54" t="s">
         <v>303</v>
       </c>
       <c r="I54" t="s">
@@ -8078,28 +8103,28 @@
         <v>704</v>
       </c>
       <c r="B131" t="s">
-        <v>134</v>
+        <v>705</v>
       </c>
       <c r="C131" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="D131" t="s">
-        <v>705</v>
+        <v>691</v>
       </c>
       <c r="E131" t="s">
+        <v>692</v>
+      </c>
+      <c r="F131" t="s">
+        <v>693</v>
+      </c>
+      <c r="G131" s="3" t="s">
         <v>706</v>
       </c>
-      <c r="F131" t="s">
+      <c r="H131" t="s">
         <v>707</v>
       </c>
-      <c r="G131" t="s">
-        <v>708</v>
-      </c>
-      <c r="H131" t="s">
-        <v>709</v>
-      </c>
       <c r="I131" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J131" t="s">
         <v>19</v>
@@ -8107,31 +8132,31 @@
     </row>
     <row r="132" spans="1:10">
       <c r="A132" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B132" t="s">
-        <v>711</v>
+        <v>134</v>
       </c>
       <c r="C132" t="s">
         <v>12</v>
       </c>
       <c r="D132" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E132" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="F132" t="s">
+        <v>711</v>
+      </c>
+      <c r="G132" t="s">
         <v>712</v>
-      </c>
-      <c r="G132" t="s">
-        <v>708</v>
       </c>
       <c r="H132" t="s">
         <v>713</v>
       </c>
       <c r="I132" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J132" t="s">
         <v>19</v>
@@ -8148,22 +8173,22 @@
         <v>12</v>
       </c>
       <c r="D133" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E133" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="F133" t="s">
+        <v>716</v>
+      </c>
+      <c r="G133" t="s">
         <v>712</v>
-      </c>
-      <c r="G133" t="s">
-        <v>716</v>
       </c>
       <c r="H133" t="s">
         <v>717</v>
       </c>
       <c r="I133" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J133" t="s">
         <v>19</v>
@@ -8180,22 +8205,22 @@
         <v>12</v>
       </c>
       <c r="D134" t="s">
+        <v>709</v>
+      </c>
+      <c r="E134" t="s">
+        <v>710</v>
+      </c>
+      <c r="F134" t="s">
+        <v>716</v>
+      </c>
+      <c r="G134" t="s">
         <v>720</v>
       </c>
-      <c r="E134" t="s">
+      <c r="H134" t="s">
         <v>721</v>
       </c>
-      <c r="F134" t="s">
-        <v>722</v>
-      </c>
-      <c r="G134" t="s">
-        <v>723</v>
-      </c>
-      <c r="H134" t="s">
-        <v>724</v>
-      </c>
       <c r="I134" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J134" t="s">
         <v>19</v>
@@ -8203,28 +8228,28 @@
     </row>
     <row r="135" spans="1:10">
       <c r="A135" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="B135" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="C135" t="s">
         <v>12</v>
       </c>
       <c r="D135" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="E135" t="s">
+        <v>725</v>
+      </c>
+      <c r="F135" t="s">
+        <v>726</v>
+      </c>
+      <c r="G135" t="s">
         <v>727</v>
       </c>
-      <c r="F135" t="s">
+      <c r="H135" t="s">
         <v>728</v>
-      </c>
-      <c r="G135" t="s">
-        <v>729</v>
-      </c>
-      <c r="H135" t="s">
-        <v>730</v>
       </c>
       <c r="I135" t="s">
         <v>19</v>
@@ -8235,28 +8260,28 @@
     </row>
     <row r="136" spans="1:10">
       <c r="A136" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B136" t="s">
-        <v>466</v>
+        <v>730</v>
       </c>
       <c r="C136" t="s">
         <v>12</v>
       </c>
       <c r="D136" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="E136" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="F136" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="G136" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H136" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="I136" t="s">
         <v>19</v>
@@ -8267,31 +8292,31 @@
     </row>
     <row r="137" spans="1:10">
       <c r="A137" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B137" t="s">
-        <v>735</v>
+        <v>466</v>
       </c>
       <c r="C137" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D137" t="s">
+        <v>724</v>
+      </c>
+      <c r="E137" t="s">
+        <v>731</v>
+      </c>
+      <c r="F137" t="s">
+        <v>732</v>
+      </c>
+      <c r="G137" t="s">
         <v>736</v>
       </c>
-      <c r="E137" t="s">
+      <c r="H137" t="s">
         <v>737</v>
       </c>
-      <c r="F137" t="s">
-        <v>738</v>
-      </c>
-      <c r="G137" t="s">
-        <v>739</v>
-      </c>
-      <c r="H137" t="s">
-        <v>740</v>
-      </c>
       <c r="I137" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J137" t="s">
         <v>19</v>
@@ -8299,31 +8324,31 @@
     </row>
     <row r="138" spans="1:10">
       <c r="A138" t="s">
+        <v>738</v>
+      </c>
+      <c r="B138" t="s">
+        <v>739</v>
+      </c>
+      <c r="C138" t="s">
+        <v>45</v>
+      </c>
+      <c r="D138" t="s">
+        <v>740</v>
+      </c>
+      <c r="E138" t="s">
         <v>741</v>
       </c>
-      <c r="B138" t="s">
+      <c r="F138" t="s">
         <v>742</v>
       </c>
-      <c r="C138" t="s">
-        <v>12</v>
-      </c>
-      <c r="D138" t="s">
+      <c r="G138" t="s">
         <v>743</v>
       </c>
-      <c r="E138" t="s">
+      <c r="H138" t="s">
         <v>744</v>
       </c>
-      <c r="F138" t="s">
-        <v>745</v>
-      </c>
-      <c r="G138" t="s">
-        <v>746</v>
-      </c>
-      <c r="H138" t="s">
-        <v>747</v>
-      </c>
       <c r="I138" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J138" t="s">
         <v>19</v>
@@ -8331,31 +8356,31 @@
     </row>
     <row r="139" spans="1:10">
       <c r="A139" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B139" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="C139" t="s">
         <v>12</v>
       </c>
       <c r="D139" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="E139" t="s">
+        <v>748</v>
+      </c>
+      <c r="F139" t="s">
+        <v>749</v>
+      </c>
+      <c r="G139" t="s">
         <v>750</v>
       </c>
-      <c r="F139" t="s">
-        <v>745</v>
-      </c>
-      <c r="G139" t="s">
+      <c r="H139" t="s">
         <v>751</v>
       </c>
-      <c r="H139" t="s">
-        <v>752</v>
-      </c>
       <c r="I139" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J139" t="s">
         <v>19</v>
@@ -8363,31 +8388,31 @@
     </row>
     <row r="140" spans="1:10">
       <c r="A140" t="s">
+        <v>752</v>
+      </c>
+      <c r="B140" t="s">
         <v>753</v>
-      </c>
-      <c r="B140" t="s">
-        <v>754</v>
       </c>
       <c r="C140" t="s">
         <v>12</v>
       </c>
       <c r="D140" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="E140" t="s">
+        <v>754</v>
+      </c>
+      <c r="F140" t="s">
+        <v>749</v>
+      </c>
+      <c r="G140" t="s">
         <v>755</v>
       </c>
-      <c r="F140" t="s">
-        <v>745</v>
-      </c>
-      <c r="G140" t="s">
+      <c r="H140" t="s">
         <v>756</v>
       </c>
-      <c r="H140" t="s">
-        <v>757</v>
-      </c>
       <c r="I140" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J140" t="s">
         <v>19</v>
@@ -8395,25 +8420,25 @@
     </row>
     <row r="141" spans="1:10">
       <c r="A141" t="s">
+        <v>757</v>
+      </c>
+      <c r="B141" t="s">
         <v>758</v>
-      </c>
-      <c r="B141" t="s">
-        <v>759</v>
       </c>
       <c r="C141" t="s">
         <v>12</v>
       </c>
       <c r="D141" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="E141" t="s">
+        <v>759</v>
+      </c>
+      <c r="F141" t="s">
+        <v>749</v>
+      </c>
+      <c r="G141" t="s">
         <v>755</v>
-      </c>
-      <c r="F141" t="s">
-        <v>745</v>
-      </c>
-      <c r="G141" t="s">
-        <v>751</v>
       </c>
       <c r="H141" t="s">
         <v>760</v>
@@ -8750,25 +8775,25 @@
         <v>819</v>
       </c>
       <c r="B152" t="s">
-        <v>820</v>
+        <v>229</v>
       </c>
       <c r="C152" t="s">
         <v>12</v>
       </c>
       <c r="D152" t="s">
+        <v>820</v>
+      </c>
+      <c r="E152" t="s">
         <v>821</v>
       </c>
-      <c r="E152" t="s">
+      <c r="F152" t="s">
         <v>822</v>
       </c>
-      <c r="F152" t="s">
+      <c r="G152" t="s">
         <v>823</v>
       </c>
-      <c r="G152" t="s">
+      <c r="H152" t="s">
         <v>824</v>
-      </c>
-      <c r="H152" t="s">
-        <v>825</v>
       </c>
       <c r="I152" t="s">
         <v>19</v>
@@ -8779,31 +8804,31 @@
     </row>
     <row r="153" spans="1:10">
       <c r="A153" t="s">
+        <v>825</v>
+      </c>
+      <c r="B153" t="s">
         <v>826</v>
-      </c>
-      <c r="B153" t="s">
-        <v>827</v>
       </c>
       <c r="C153" t="s">
         <v>12</v>
       </c>
       <c r="D153" t="s">
+        <v>820</v>
+      </c>
+      <c r="E153" t="s">
         <v>821</v>
       </c>
-      <c r="E153" t="s">
+      <c r="F153" t="s">
         <v>822</v>
       </c>
-      <c r="F153" t="s">
-        <v>823</v>
-      </c>
       <c r="G153" t="s">
+        <v>827</v>
+      </c>
+      <c r="H153" t="s">
         <v>828</v>
       </c>
-      <c r="H153" t="s">
-        <v>829</v>
-      </c>
       <c r="I153" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J153" t="s">
         <v>19</v>
@@ -8811,31 +8836,31 @@
     </row>
     <row r="154" spans="1:10">
       <c r="A154" t="s">
+        <v>829</v>
+      </c>
+      <c r="B154" t="s">
         <v>830</v>
-      </c>
-      <c r="B154" t="s">
-        <v>831</v>
       </c>
       <c r="C154" t="s">
         <v>12</v>
       </c>
       <c r="D154" t="s">
+        <v>820</v>
+      </c>
+      <c r="E154" t="s">
+        <v>821</v>
+      </c>
+      <c r="F154" t="s">
+        <v>822</v>
+      </c>
+      <c r="G154" t="s">
+        <v>831</v>
+      </c>
+      <c r="H154" t="s">
         <v>832</v>
       </c>
-      <c r="E154" t="s">
-        <v>833</v>
-      </c>
-      <c r="F154" t="s">
-        <v>834</v>
-      </c>
-      <c r="G154" t="s">
-        <v>835</v>
-      </c>
-      <c r="H154" t="s">
-        <v>836</v>
-      </c>
       <c r="I154" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J154" t="s">
         <v>19</v>
@@ -8843,31 +8868,31 @@
     </row>
     <row r="155" spans="1:10">
       <c r="A155" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="B155" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="C155" t="s">
         <v>12</v>
       </c>
       <c r="D155" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="E155" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="F155" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="G155" t="s">
+        <v>838</v>
+      </c>
+      <c r="H155" t="s">
         <v>839</v>
       </c>
-      <c r="H155" t="s">
-        <v>840</v>
-      </c>
       <c r="I155" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J155" t="s">
         <v>19</v>
@@ -8875,22 +8900,22 @@
     </row>
     <row r="156" spans="1:10">
       <c r="A156" t="s">
+        <v>840</v>
+      </c>
+      <c r="B156" t="s">
         <v>841</v>
-      </c>
-      <c r="B156" t="s">
-        <v>539</v>
       </c>
       <c r="C156" t="s">
         <v>12</v>
       </c>
       <c r="D156" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="E156" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="F156" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="G156" t="s">
         <v>842</v>
@@ -8899,7 +8924,7 @@
         <v>843</v>
       </c>
       <c r="I156" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J156" t="s">
         <v>19</v>
@@ -8910,28 +8935,28 @@
         <v>844</v>
       </c>
       <c r="B157" t="s">
-        <v>44</v>
+        <v>539</v>
       </c>
       <c r="C157" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D157" t="s">
+        <v>835</v>
+      </c>
+      <c r="E157" t="s">
+        <v>836</v>
+      </c>
+      <c r="F157" t="s">
+        <v>837</v>
+      </c>
+      <c r="G157" t="s">
         <v>845</v>
       </c>
-      <c r="E157" t="s">
+      <c r="H157" t="s">
         <v>846</v>
       </c>
-      <c r="F157" t="s">
-        <v>847</v>
-      </c>
-      <c r="G157" t="s">
-        <v>848</v>
-      </c>
-      <c r="H157" t="s">
-        <v>849</v>
-      </c>
       <c r="I157" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J157" t="s">
         <v>19</v>
@@ -8939,31 +8964,31 @@
     </row>
     <row r="158" spans="1:10">
       <c r="A158" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="B158" t="s">
-        <v>851</v>
+        <v>44</v>
       </c>
       <c r="C158" t="s">
         <v>45</v>
       </c>
       <c r="D158" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="E158" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="F158" t="s">
+        <v>850</v>
+      </c>
+      <c r="G158" t="s">
+        <v>851</v>
+      </c>
+      <c r="H158" t="s">
         <v>852</v>
       </c>
-      <c r="G158" t="s">
-        <v>853</v>
-      </c>
-      <c r="H158" t="s">
-        <v>854</v>
-      </c>
       <c r="I158" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J158" t="s">
         <v>19</v>
@@ -8971,28 +8996,28 @@
     </row>
     <row r="159" spans="1:10">
       <c r="A159" t="s">
+        <v>853</v>
+      </c>
+      <c r="B159" t="s">
+        <v>854</v>
+      </c>
+      <c r="C159" t="s">
+        <v>45</v>
+      </c>
+      <c r="D159" t="s">
+        <v>848</v>
+      </c>
+      <c r="E159" t="s">
+        <v>849</v>
+      </c>
+      <c r="F159" t="s">
         <v>855</v>
       </c>
-      <c r="B159" t="s">
+      <c r="G159" t="s">
         <v>856</v>
       </c>
-      <c r="C159" t="s">
-        <v>27</v>
-      </c>
-      <c r="D159" t="s">
+      <c r="H159" t="s">
         <v>857</v>
-      </c>
-      <c r="E159" t="s">
-        <v>858</v>
-      </c>
-      <c r="F159" t="s">
-        <v>859</v>
-      </c>
-      <c r="G159" t="s">
-        <v>860</v>
-      </c>
-      <c r="H159" t="s">
-        <v>861</v>
       </c>
       <c r="I159" t="s">
         <v>19</v>
@@ -9003,28 +9028,28 @@
     </row>
     <row r="160" spans="1:10">
       <c r="A160" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="B160" t="s">
-        <v>466</v>
+        <v>859</v>
       </c>
       <c r="C160" t="s">
         <v>27</v>
       </c>
       <c r="D160" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="E160" t="s">
+        <v>861</v>
+      </c>
+      <c r="F160" t="s">
+        <v>862</v>
+      </c>
+      <c r="G160" t="s">
         <v>863</v>
       </c>
-      <c r="F160" t="s">
+      <c r="H160" t="s">
         <v>864</v>
-      </c>
-      <c r="G160" t="s">
-        <v>865</v>
-      </c>
-      <c r="H160" t="s">
-        <v>866</v>
       </c>
       <c r="I160" t="s">
         <v>19</v>
@@ -9035,28 +9060,28 @@
     </row>
     <row r="161" spans="1:10">
       <c r="A161" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B161" t="s">
-        <v>868</v>
+        <v>466</v>
       </c>
       <c r="C161" t="s">
         <v>27</v>
       </c>
       <c r="D161" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="E161" t="s">
+        <v>866</v>
+      </c>
+      <c r="F161" t="s">
+        <v>867</v>
+      </c>
+      <c r="G161" t="s">
+        <v>868</v>
+      </c>
+      <c r="H161" t="s">
         <v>869</v>
-      </c>
-      <c r="F161" t="s">
-        <v>870</v>
-      </c>
-      <c r="G161" t="s">
-        <v>871</v>
-      </c>
-      <c r="H161" t="s">
-        <v>872</v>
       </c>
       <c r="I161" t="s">
         <v>19</v>
@@ -9067,28 +9092,28 @@
     </row>
     <row r="162" spans="1:10">
       <c r="A162" t="s">
+        <v>870</v>
+      </c>
+      <c r="B162" t="s">
+        <v>871</v>
+      </c>
+      <c r="C162" t="s">
+        <v>27</v>
+      </c>
+      <c r="D162" t="s">
+        <v>860</v>
+      </c>
+      <c r="E162" t="s">
+        <v>872</v>
+      </c>
+      <c r="F162" t="s">
         <v>873</v>
       </c>
-      <c r="B162" t="s">
-        <v>134</v>
-      </c>
-      <c r="C162" t="s">
-        <v>12</v>
-      </c>
-      <c r="D162" t="s">
+      <c r="G162" t="s">
         <v>874</v>
       </c>
-      <c r="E162" t="s">
+      <c r="H162" t="s">
         <v>875</v>
-      </c>
-      <c r="F162" t="s">
-        <v>876</v>
-      </c>
-      <c r="G162" t="s">
-        <v>877</v>
-      </c>
-      <c r="H162" t="s">
-        <v>878</v>
       </c>
       <c r="I162" t="s">
         <v>19</v>
@@ -9099,28 +9124,28 @@
     </row>
     <row r="163" spans="1:10">
       <c r="A163" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="B163" t="s">
-        <v>880</v>
+        <v>134</v>
       </c>
       <c r="C163" t="s">
         <v>12</v>
       </c>
       <c r="D163" t="s">
+        <v>877</v>
+      </c>
+      <c r="E163" t="s">
+        <v>878</v>
+      </c>
+      <c r="F163" t="s">
+        <v>879</v>
+      </c>
+      <c r="G163" t="s">
+        <v>880</v>
+      </c>
+      <c r="H163" t="s">
         <v>881</v>
-      </c>
-      <c r="E163" t="s">
-        <v>875</v>
-      </c>
-      <c r="F163" t="s">
-        <v>876</v>
-      </c>
-      <c r="G163" t="s">
-        <v>882</v>
-      </c>
-      <c r="H163" t="s">
-        <v>883</v>
       </c>
       <c r="I163" t="s">
         <v>19</v>
@@ -9131,28 +9156,28 @@
     </row>
     <row r="164" spans="1:10">
       <c r="A164" t="s">
+        <v>882</v>
+      </c>
+      <c r="B164" t="s">
+        <v>883</v>
+      </c>
+      <c r="C164" t="s">
+        <v>12</v>
+      </c>
+      <c r="D164" t="s">
         <v>884</v>
       </c>
-      <c r="B164" t="s">
+      <c r="E164" t="s">
+        <v>878</v>
+      </c>
+      <c r="F164" t="s">
+        <v>879</v>
+      </c>
+      <c r="G164" t="s">
         <v>885</v>
       </c>
-      <c r="C164" t="s">
-        <v>27</v>
-      </c>
-      <c r="D164" t="s">
+      <c r="H164" t="s">
         <v>886</v>
-      </c>
-      <c r="E164" t="s">
-        <v>887</v>
-      </c>
-      <c r="F164" t="s">
-        <v>888</v>
-      </c>
-      <c r="G164" t="s">
-        <v>889</v>
-      </c>
-      <c r="H164" t="s">
-        <v>890</v>
       </c>
       <c r="I164" t="s">
         <v>19</v>
@@ -9163,22 +9188,22 @@
     </row>
     <row r="165" spans="1:10">
       <c r="A165" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="B165" t="s">
-        <v>466</v>
+        <v>888</v>
       </c>
       <c r="C165" t="s">
         <v>27</v>
       </c>
       <c r="D165" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="E165" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="F165" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="G165" t="s">
         <v>892</v>
@@ -9190,7 +9215,7 @@
         <v>19</v>
       </c>
       <c r="J165" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="166" spans="1:10">
@@ -9198,57 +9223,57 @@
         <v>894</v>
       </c>
       <c r="B166" t="s">
-        <v>895</v>
+        <v>466</v>
       </c>
       <c r="C166" t="s">
         <v>27</v>
       </c>
       <c r="D166" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="E166" t="s">
+        <v>890</v>
+      </c>
+      <c r="F166" t="s">
+        <v>891</v>
+      </c>
+      <c r="G166" t="s">
+        <v>895</v>
+      </c>
+      <c r="H166" t="s">
         <v>896</v>
       </c>
-      <c r="F166" t="s">
-        <v>897</v>
-      </c>
-      <c r="G166" t="s">
-        <v>898</v>
-      </c>
-      <c r="H166" t="s">
-        <v>899</v>
-      </c>
       <c r="I166" t="s">
         <v>19</v>
       </c>
       <c r="J166" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="167" spans="1:10">
       <c r="A167" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="B167" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="C167" t="s">
         <v>27</v>
       </c>
       <c r="D167" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="E167" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="F167" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="G167" t="s">
+        <v>901</v>
+      </c>
+      <c r="H167" t="s">
         <v>902</v>
-      </c>
-      <c r="H167" t="s">
-        <v>903</v>
       </c>
       <c r="I167" t="s">
         <v>19</v>
@@ -9259,31 +9284,31 @@
     </row>
     <row r="168" spans="1:10">
       <c r="A168" t="s">
+        <v>903</v>
+      </c>
+      <c r="B168" t="s">
         <v>904</v>
-      </c>
-      <c r="B168" t="s">
-        <v>905</v>
       </c>
       <c r="C168" t="s">
         <v>27</v>
       </c>
       <c r="D168" t="s">
+        <v>889</v>
+      </c>
+      <c r="E168" t="s">
+        <v>899</v>
+      </c>
+      <c r="F168" t="s">
+        <v>900</v>
+      </c>
+      <c r="G168" t="s">
+        <v>905</v>
+      </c>
+      <c r="H168" t="s">
         <v>906</v>
       </c>
-      <c r="E168" t="s">
-        <v>907</v>
-      </c>
-      <c r="F168" t="s">
-        <v>908</v>
-      </c>
-      <c r="G168" t="s">
-        <v>909</v>
-      </c>
-      <c r="H168" t="s">
-        <v>910</v>
-      </c>
       <c r="I168" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J168" t="s">
         <v>19</v>
@@ -9291,31 +9316,31 @@
     </row>
     <row r="169" spans="1:10">
       <c r="A169" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="B169" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="C169" t="s">
         <v>27</v>
       </c>
       <c r="D169" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="E169" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="F169" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="G169" t="s">
+        <v>912</v>
+      </c>
+      <c r="H169" t="s">
         <v>913</v>
       </c>
-      <c r="H169" t="s">
-        <v>914</v>
-      </c>
       <c r="I169" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J169" t="s">
         <v>19</v>
@@ -9323,31 +9348,31 @@
     </row>
     <row r="170" spans="1:10">
       <c r="A170" t="s">
+        <v>914</v>
+      </c>
+      <c r="B170" t="s">
         <v>915</v>
       </c>
-      <c r="B170" t="s">
+      <c r="C170" t="s">
+        <v>27</v>
+      </c>
+      <c r="D170" t="s">
+        <v>909</v>
+      </c>
+      <c r="E170" t="s">
+        <v>910</v>
+      </c>
+      <c r="F170" t="s">
+        <v>911</v>
+      </c>
+      <c r="G170" t="s">
         <v>916</v>
       </c>
-      <c r="C170" t="s">
-        <v>12</v>
-      </c>
-      <c r="D170" t="s">
+      <c r="H170" t="s">
         <v>917</v>
       </c>
-      <c r="E170" t="s">
-        <v>918</v>
-      </c>
-      <c r="F170" t="s">
-        <v>919</v>
-      </c>
-      <c r="G170" t="s">
-        <v>920</v>
-      </c>
-      <c r="H170" t="s">
-        <v>921</v>
-      </c>
       <c r="I170" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J170" t="s">
         <v>19</v>
@@ -9355,22 +9380,22 @@
     </row>
     <row r="171" spans="1:10">
       <c r="A171" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="B171" t="s">
-        <v>337</v>
+        <v>919</v>
       </c>
       <c r="C171" t="s">
         <v>12</v>
       </c>
       <c r="D171" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="E171" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="F171" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="G171" t="s">
         <v>923</v>
@@ -9379,7 +9404,7 @@
         <v>924</v>
       </c>
       <c r="I171" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J171" t="s">
         <v>19</v>
@@ -9390,22 +9415,22 @@
         <v>925</v>
       </c>
       <c r="B172" t="s">
-        <v>926</v>
+        <v>337</v>
       </c>
       <c r="C172" t="s">
         <v>12</v>
       </c>
       <c r="D172" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="E172" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="F172" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="G172" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="H172" t="s">
         <v>927</v>
@@ -9422,25 +9447,25 @@
         <v>928</v>
       </c>
       <c r="B173" t="s">
-        <v>191</v>
+        <v>929</v>
       </c>
       <c r="C173" t="s">
         <v>12</v>
       </c>
       <c r="D173" t="s">
-        <v>929</v>
+        <v>920</v>
       </c>
       <c r="E173" t="s">
+        <v>921</v>
+      </c>
+      <c r="F173" t="s">
+        <v>922</v>
+      </c>
+      <c r="G173" t="s">
+        <v>926</v>
+      </c>
+      <c r="H173" t="s">
         <v>930</v>
-      </c>
-      <c r="F173" t="s">
-        <v>931</v>
-      </c>
-      <c r="G173" t="s">
-        <v>932</v>
-      </c>
-      <c r="H173" t="s">
-        <v>933</v>
       </c>
       <c r="I173" t="s">
         <v>19</v>
@@ -9451,28 +9476,28 @@
     </row>
     <row r="174" spans="1:10">
       <c r="A174" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="B174" t="s">
-        <v>935</v>
+        <v>191</v>
       </c>
       <c r="C174" t="s">
         <v>12</v>
       </c>
       <c r="D174" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E174" t="s">
+        <v>933</v>
+      </c>
+      <c r="F174" t="s">
+        <v>934</v>
+      </c>
+      <c r="G174" t="s">
+        <v>935</v>
+      </c>
+      <c r="H174" t="s">
         <v>936</v>
-      </c>
-      <c r="F174" t="s">
-        <v>937</v>
-      </c>
-      <c r="G174" t="s">
-        <v>938</v>
-      </c>
-      <c r="H174" t="s">
-        <v>939</v>
       </c>
       <c r="I174" t="s">
         <v>19</v>
@@ -9483,22 +9508,22 @@
     </row>
     <row r="175" spans="1:10">
       <c r="A175" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="B175" t="s">
-        <v>236</v>
+        <v>938</v>
       </c>
       <c r="C175" t="s">
         <v>12</v>
       </c>
       <c r="D175" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E175" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="F175" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="G175" t="s">
         <v>941</v>
@@ -9518,25 +9543,25 @@
         <v>943</v>
       </c>
       <c r="B176" t="s">
-        <v>944</v>
+        <v>236</v>
       </c>
       <c r="C176" t="s">
         <v>12</v>
       </c>
       <c r="D176" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E176" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="F176" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="G176" t="s">
+        <v>944</v>
+      </c>
+      <c r="H176" t="s">
         <v>945</v>
-      </c>
-      <c r="H176" t="s">
-        <v>946</v>
       </c>
       <c r="I176" t="s">
         <v>19</v>
@@ -9547,28 +9572,28 @@
     </row>
     <row r="177" spans="1:10">
       <c r="A177" t="s">
+        <v>946</v>
+      </c>
+      <c r="B177" t="s">
         <v>947</v>
-      </c>
-      <c r="B177" t="s">
-        <v>948</v>
       </c>
       <c r="C177" t="s">
         <v>12</v>
       </c>
       <c r="D177" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E177" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="F177" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="G177" t="s">
+        <v>948</v>
+      </c>
+      <c r="H177" t="s">
         <v>949</v>
-      </c>
-      <c r="H177" t="s">
-        <v>950</v>
       </c>
       <c r="I177" t="s">
         <v>19</v>
@@ -9579,31 +9604,31 @@
     </row>
     <row r="178" spans="1:10">
       <c r="A178" t="s">
+        <v>950</v>
+      </c>
+      <c r="B178" t="s">
         <v>951</v>
       </c>
-      <c r="B178" t="s">
+      <c r="C178" t="s">
+        <v>12</v>
+      </c>
+      <c r="D178" t="s">
+        <v>932</v>
+      </c>
+      <c r="E178" t="s">
+        <v>939</v>
+      </c>
+      <c r="F178" t="s">
+        <v>940</v>
+      </c>
+      <c r="G178" t="s">
         <v>952</v>
       </c>
-      <c r="C178" t="s">
-        <v>45</v>
-      </c>
-      <c r="D178" t="s">
+      <c r="H178" t="s">
         <v>953</v>
       </c>
-      <c r="E178" t="s">
-        <v>954</v>
-      </c>
-      <c r="F178" t="s">
-        <v>955</v>
-      </c>
-      <c r="G178" t="s">
-        <v>956</v>
-      </c>
-      <c r="H178" t="s">
-        <v>957</v>
-      </c>
       <c r="I178" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J178" t="s">
         <v>19</v>
@@ -9611,31 +9636,31 @@
     </row>
     <row r="179" spans="1:10">
       <c r="A179" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="B179" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="C179" t="s">
         <v>45</v>
       </c>
       <c r="D179" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="E179" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="F179" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="G179" t="s">
+        <v>959</v>
+      </c>
+      <c r="H179" t="s">
         <v>960</v>
       </c>
-      <c r="H179" t="s">
-        <v>961</v>
-      </c>
       <c r="I179" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J179" t="s">
         <v>19</v>
@@ -9643,28 +9668,28 @@
     </row>
     <row r="180" spans="1:10">
       <c r="A180" t="s">
+        <v>961</v>
+      </c>
+      <c r="B180" t="s">
         <v>962</v>
-      </c>
-      <c r="B180" t="s">
-        <v>963</v>
       </c>
       <c r="C180" t="s">
         <v>45</v>
       </c>
       <c r="D180" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="E180" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="F180" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="G180" t="s">
+        <v>963</v>
+      </c>
+      <c r="H180" t="s">
         <v>964</v>
-      </c>
-      <c r="H180" t="s">
-        <v>965</v>
       </c>
       <c r="I180" t="s">
         <v>19</v>
@@ -9675,28 +9700,28 @@
     </row>
     <row r="181" spans="1:10">
       <c r="A181" t="s">
+        <v>965</v>
+      </c>
+      <c r="B181" t="s">
         <v>966</v>
       </c>
-      <c r="B181" t="s">
+      <c r="C181" t="s">
+        <v>45</v>
+      </c>
+      <c r="D181" t="s">
+        <v>956</v>
+      </c>
+      <c r="E181" t="s">
+        <v>957</v>
+      </c>
+      <c r="F181" t="s">
+        <v>958</v>
+      </c>
+      <c r="G181" t="s">
         <v>967</v>
       </c>
-      <c r="C181" t="s">
-        <v>27</v>
-      </c>
-      <c r="D181" t="s">
+      <c r="H181" t="s">
         <v>968</v>
-      </c>
-      <c r="E181" t="s">
-        <v>969</v>
-      </c>
-      <c r="F181" t="s">
-        <v>970</v>
-      </c>
-      <c r="G181" t="s">
-        <v>971</v>
-      </c>
-      <c r="H181" t="s">
-        <v>972</v>
       </c>
       <c r="I181" t="s">
         <v>19</v>
@@ -9707,31 +9732,31 @@
     </row>
     <row r="182" spans="1:10">
       <c r="A182" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="B182" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="C182" t="s">
         <v>27</v>
       </c>
       <c r="D182" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="E182" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="F182" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="G182" t="s">
+        <v>974</v>
+      </c>
+      <c r="H182" t="s">
         <v>975</v>
       </c>
-      <c r="H182" t="s">
-        <v>976</v>
-      </c>
       <c r="I182" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J182" t="s">
         <v>19</v>
@@ -9739,28 +9764,28 @@
     </row>
     <row r="183" spans="1:10">
       <c r="A183" t="s">
+        <v>976</v>
+      </c>
+      <c r="B183" t="s">
         <v>977</v>
-      </c>
-      <c r="B183" t="s">
-        <v>978</v>
       </c>
       <c r="C183" t="s">
         <v>27</v>
       </c>
       <c r="D183" t="s">
+        <v>971</v>
+      </c>
+      <c r="E183" t="s">
+        <v>972</v>
+      </c>
+      <c r="F183" t="s">
+        <v>973</v>
+      </c>
+      <c r="G183" t="s">
+        <v>978</v>
+      </c>
+      <c r="H183" t="s">
         <v>979</v>
-      </c>
-      <c r="E183" t="s">
-        <v>980</v>
-      </c>
-      <c r="F183" t="s">
-        <v>931</v>
-      </c>
-      <c r="G183" t="s">
-        <v>981</v>
-      </c>
-      <c r="H183" t="s">
-        <v>982</v>
       </c>
       <c r="I183" t="s">
         <v>18</v>
@@ -9771,31 +9796,31 @@
     </row>
     <row r="184" spans="1:10">
       <c r="A184" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="B184" t="s">
-        <v>229</v>
+        <v>981</v>
       </c>
       <c r="C184" t="s">
         <v>27</v>
       </c>
       <c r="D184" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="E184" t="s">
+        <v>983</v>
+      </c>
+      <c r="F184" t="s">
+        <v>934</v>
+      </c>
+      <c r="G184" t="s">
         <v>984</v>
       </c>
-      <c r="F184" t="s">
+      <c r="H184" t="s">
         <v>985</v>
       </c>
-      <c r="G184" t="s">
-        <v>986</v>
-      </c>
-      <c r="H184" t="s">
-        <v>987</v>
-      </c>
       <c r="I184" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J184" t="s">
         <v>19</v>
@@ -9803,39 +9828,71 @@
     </row>
     <row r="185" spans="1:10">
       <c r="A185" t="s">
+        <v>986</v>
+      </c>
+      <c r="B185" t="s">
+        <v>229</v>
+      </c>
+      <c r="C185" t="s">
+        <v>27</v>
+      </c>
+      <c r="D185" t="s">
+        <v>982</v>
+      </c>
+      <c r="E185" t="s">
+        <v>987</v>
+      </c>
+      <c r="F185" t="s">
         <v>988</v>
       </c>
-      <c r="B185" t="s">
+      <c r="G185" t="s">
+        <v>989</v>
+      </c>
+      <c r="H185" t="s">
+        <v>990</v>
+      </c>
+      <c r="I185" t="s">
+        <v>19</v>
+      </c>
+      <c r="J185" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10">
+      <c r="A186" t="s">
+        <v>991</v>
+      </c>
+      <c r="B186" t="s">
         <v>466</v>
       </c>
-      <c r="C185" t="s">
+      <c r="C186" t="s">
         <v>45</v>
       </c>
-      <c r="D185" t="s">
-        <v>989</v>
-      </c>
-      <c r="E185" t="s">
-        <v>990</v>
-      </c>
-      <c r="F185" t="s">
-        <v>991</v>
-      </c>
-      <c r="G185" t="s">
+      <c r="D186" t="s">
         <v>992</v>
       </c>
-      <c r="H185" t="s">
+      <c r="E186" t="s">
         <v>993</v>
       </c>
-      <c r="I185" t="s">
-        <v>19</v>
-      </c>
-      <c r="J185" t="s">
+      <c r="F186" t="s">
+        <v>994</v>
+      </c>
+      <c r="G186" t="s">
+        <v>995</v>
+      </c>
+      <c r="H186" t="s">
+        <v>996</v>
+      </c>
+      <c r="I186" t="s">
+        <v>19</v>
+      </c>
+      <c r="J186" t="s">
         <v>19</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J185">
-    <sortCondition ref="D2:D185"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J186">
+    <sortCondition ref="D2:D186"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -9913,7 +9970,7 @@
         <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="I2" t="s">
         <v>18</v>
@@ -11524,7 +11581,7 @@
     </row>
     <row r="53" spans="1:10">
       <c r="A53" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="B53" t="s">
         <v>134</v>
@@ -11533,19 +11590,19 @@
         <v>12</v>
       </c>
       <c r="D53" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E53" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="F53" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="G53" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="H53" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="I53" t="s">
         <v>18</v>
@@ -11556,28 +11613,28 @@
     </row>
     <row r="54" spans="1:10">
       <c r="A54" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="B54" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="C54" t="s">
         <v>12</v>
       </c>
       <c r="D54" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E54" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="F54" t="s">
+        <v>716</v>
+      </c>
+      <c r="G54" t="s">
         <v>712</v>
       </c>
-      <c r="G54" t="s">
-        <v>708</v>
-      </c>
       <c r="H54" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="I54" t="s">
         <v>19</v>
@@ -11588,28 +11645,28 @@
     </row>
     <row r="55" spans="1:10">
       <c r="A55" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="B55" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="C55" t="s">
         <v>12</v>
       </c>
       <c r="D55" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E55" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="F55" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="G55" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="H55" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="I55" t="s">
         <v>18</v>
@@ -11620,28 +11677,28 @@
     </row>
     <row r="56" spans="1:10">
       <c r="A56" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="B56" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C56" t="s">
         <v>12</v>
       </c>
       <c r="D56" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="E56" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="F56" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="G56" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="H56" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="I56" t="s">
         <v>19</v>
@@ -11652,28 +11709,28 @@
     </row>
     <row r="57" spans="1:10">
       <c r="A57" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="B57" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="C57" t="s">
         <v>12</v>
       </c>
       <c r="D57" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="E57" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="F57" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="G57" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="H57" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="I57" t="s">
         <v>19</v>
@@ -11684,7 +11741,7 @@
     </row>
     <row r="58" spans="1:10">
       <c r="A58" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="B58" t="s">
         <v>466</v>
@@ -11693,19 +11750,19 @@
         <v>12</v>
       </c>
       <c r="D58" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="E58" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="F58" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="G58" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="H58" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="I58" t="s">
         <v>19</v>
@@ -11716,28 +11773,28 @@
     </row>
     <row r="59" spans="1:10">
       <c r="A59" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="B59" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="C59" t="s">
         <v>12</v>
       </c>
       <c r="D59" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="E59" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="F59" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="G59" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="H59" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="I59" t="s">
         <v>19</v>
@@ -11748,28 +11805,28 @@
     </row>
     <row r="60" spans="1:10">
       <c r="A60" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="B60" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="C60" t="s">
         <v>12</v>
       </c>
       <c r="D60" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="E60" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="F60" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="G60" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="H60" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="I60" t="s">
         <v>18</v>
@@ -11780,28 +11837,28 @@
     </row>
     <row r="61" spans="1:10">
       <c r="A61" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="B61" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="C61" t="s">
         <v>12</v>
       </c>
       <c r="D61" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="E61" t="s">
+        <v>759</v>
+      </c>
+      <c r="F61" t="s">
+        <v>749</v>
+      </c>
+      <c r="G61" t="s">
         <v>755</v>
       </c>
-      <c r="F61" t="s">
-        <v>745</v>
-      </c>
-      <c r="G61" t="s">
-        <v>756</v>
-      </c>
       <c r="H61" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="I61" t="s">
         <v>19</v>
@@ -11812,28 +11869,28 @@
     </row>
     <row r="62" spans="1:10">
       <c r="A62" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="B62" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="C62" t="s">
         <v>12</v>
       </c>
       <c r="D62" t="s">
-        <v>743</v>
+        <v>763</v>
       </c>
       <c r="E62" t="s">
-        <v>755</v>
+        <v>764</v>
       </c>
       <c r="F62" t="s">
-        <v>745</v>
+        <v>765</v>
       </c>
       <c r="G62" t="s">
-        <v>751</v>
+        <v>766</v>
       </c>
       <c r="H62" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="I62" t="s">
         <v>19</v>
@@ -11844,10 +11901,10 @@
     </row>
     <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="B63" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="C63" t="s">
         <v>12</v>
@@ -11856,80 +11913,80 @@
         <v>763</v>
       </c>
       <c r="E63" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="F63" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="G63" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="H63" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="I63" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J63" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>768</v>
+        <v>819</v>
       </c>
       <c r="B64" t="s">
-        <v>769</v>
+        <v>229</v>
       </c>
       <c r="C64" t="s">
         <v>12</v>
       </c>
       <c r="D64" t="s">
-        <v>763</v>
+        <v>820</v>
       </c>
       <c r="E64" t="s">
-        <v>770</v>
+        <v>821</v>
       </c>
       <c r="F64" t="s">
-        <v>771</v>
+        <v>822</v>
       </c>
       <c r="G64" t="s">
-        <v>772</v>
+        <v>823</v>
       </c>
       <c r="H64" t="s">
-        <v>773</v>
+        <v>824</v>
       </c>
       <c r="I64" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J64" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="B65" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="C65" t="s">
         <v>12</v>
       </c>
       <c r="D65" t="s">
+        <v>820</v>
+      </c>
+      <c r="E65" t="s">
         <v>821</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>822</v>
       </c>
-      <c r="F65" t="s">
-        <v>823</v>
-      </c>
       <c r="G65" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="H65" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="I65" t="s">
         <v>19</v>
@@ -11940,28 +11997,28 @@
     </row>
     <row r="66" spans="1:10">
       <c r="A66" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="B66" t="s">
-        <v>827</v>
+        <v>998</v>
       </c>
       <c r="C66" t="s">
         <v>12</v>
       </c>
       <c r="D66" t="s">
+        <v>820</v>
+      </c>
+      <c r="E66" t="s">
         <v>821</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>822</v>
       </c>
-      <c r="F66" t="s">
-        <v>823</v>
-      </c>
       <c r="G66" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="H66" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="I66" t="s">
         <v>18</v>
@@ -11972,28 +12029,28 @@
     </row>
     <row r="67" spans="1:10">
       <c r="A67" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="B67" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="C67" t="s">
         <v>12</v>
       </c>
       <c r="D67" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="E67" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="F67" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="G67" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="H67" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="I67" t="s">
         <v>19</v>
@@ -12004,28 +12061,28 @@
     </row>
     <row r="68" spans="1:10">
       <c r="A68" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="B68" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="C68" t="s">
         <v>12</v>
       </c>
       <c r="D68" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="E68" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="F68" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="G68" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="H68" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="I68" t="s">
         <v>18</v>
@@ -12036,7 +12093,7 @@
     </row>
     <row r="69" spans="1:10">
       <c r="A69" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="B69" t="s">
         <v>539</v>
@@ -12045,19 +12102,19 @@
         <v>12</v>
       </c>
       <c r="D69" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="E69" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="F69" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="G69" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="H69" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="I69" t="s">
         <v>19</v>
@@ -12068,7 +12125,7 @@
     </row>
     <row r="70" spans="1:10">
       <c r="A70" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="B70" t="s">
         <v>134</v>
@@ -12077,19 +12134,19 @@
         <v>12</v>
       </c>
       <c r="D70" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="E70" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="F70" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="G70" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="H70" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="I70" t="s">
         <v>19</v>
@@ -12100,28 +12157,28 @@
     </row>
     <row r="71" spans="1:10">
       <c r="A71" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="B71" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="C71" t="s">
         <v>12</v>
       </c>
       <c r="D71" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="E71" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="F71" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="G71" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="H71" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="I71" t="s">
         <v>19</v>
@@ -12132,28 +12189,28 @@
     </row>
     <row r="72" spans="1:10">
       <c r="A72" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="B72" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="C72" t="s">
         <v>12</v>
       </c>
       <c r="D72" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="E72" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="F72" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="G72" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="H72" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="I72" t="s">
         <v>18</v>
@@ -12164,7 +12221,7 @@
     </row>
     <row r="73" spans="1:10">
       <c r="A73" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="B73" t="s">
         <v>337</v>
@@ -12173,19 +12230,19 @@
         <v>12</v>
       </c>
       <c r="D73" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="E73" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="F73" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="G73" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="H73" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="I73" t="s">
         <v>19</v>
@@ -12196,28 +12253,28 @@
     </row>
     <row r="74" spans="1:10">
       <c r="A74" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="B74" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="C74" t="s">
         <v>12</v>
       </c>
       <c r="D74" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="E74" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="F74" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="G74" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="H74" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="I74" t="s">
         <v>19</v>
@@ -12228,7 +12285,7 @@
     </row>
     <row r="75" spans="1:10">
       <c r="A75" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="B75" t="s">
         <v>191</v>
@@ -12237,19 +12294,19 @@
         <v>12</v>
       </c>
       <c r="D75" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E75" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="F75" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="G75" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="H75" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="I75" t="s">
         <v>19</v>
@@ -12260,28 +12317,28 @@
     </row>
     <row r="76" spans="1:10">
       <c r="A76" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="B76" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="C76" t="s">
         <v>12</v>
       </c>
       <c r="D76" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E76" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="F76" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="G76" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="H76" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="I76" t="s">
         <v>19</v>
@@ -12292,7 +12349,7 @@
     </row>
     <row r="77" spans="1:10">
       <c r="A77" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="B77" t="s">
         <v>236</v>
@@ -12301,19 +12358,19 @@
         <v>12</v>
       </c>
       <c r="D77" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E77" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="F77" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="G77" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="H77" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="I77" t="s">
         <v>19</v>
@@ -12324,28 +12381,28 @@
     </row>
     <row r="78" spans="1:10">
       <c r="A78" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="B78" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="C78" t="s">
         <v>12</v>
       </c>
       <c r="D78" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E78" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="F78" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="G78" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="H78" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="I78" t="s">
         <v>19</v>
@@ -12356,28 +12413,28 @@
     </row>
     <row r="79" spans="1:10">
       <c r="A79" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="B79" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="C79" t="s">
         <v>12</v>
       </c>
       <c r="D79" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E79" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="F79" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="G79" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="H79" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="I79" t="s">
         <v>19</v>
@@ -12396,7 +12453,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
@@ -12607,7 +12664,7 @@
         <v>158</v>
       </c>
       <c r="B7" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="C7" t="s">
         <v>45</v>
@@ -13064,13 +13121,13 @@
         <v>284</v>
       </c>
       <c r="E21" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="F21" t="s">
         <v>286</v>
       </c>
       <c r="G21" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="H21" t="s">
         <v>288</v>
@@ -13136,7 +13193,7 @@
       <c r="G23" t="s">
         <v>302</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="H23" t="s">
         <v>303</v>
       </c>
       <c r="I23" t="s">
@@ -13596,10 +13653,10 @@
     </row>
     <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="B38" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="C38" t="s">
         <v>45</v>
@@ -13614,10 +13671,10 @@
         <v>693</v>
       </c>
       <c r="G38" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="H38" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="I38" t="s">
         <v>19</v>
@@ -13724,31 +13781,31 @@
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>734</v>
+        <v>704</v>
       </c>
       <c r="B42" t="s">
-        <v>735</v>
+        <v>705</v>
       </c>
       <c r="C42" t="s">
         <v>45</v>
       </c>
       <c r="D42" t="s">
-        <v>736</v>
+        <v>691</v>
       </c>
       <c r="E42" t="s">
-        <v>737</v>
+        <v>692</v>
       </c>
       <c r="F42" t="s">
-        <v>738</v>
-      </c>
-      <c r="G42" t="s">
-        <v>739</v>
+        <v>693</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>706</v>
       </c>
       <c r="H42" t="s">
-        <v>740</v>
+        <v>707</v>
       </c>
       <c r="I42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J42" t="s">
         <v>19</v>
@@ -13756,31 +13813,31 @@
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>813</v>
+        <v>738</v>
       </c>
       <c r="B43" t="s">
-        <v>814</v>
+        <v>739</v>
       </c>
       <c r="C43" t="s">
         <v>45</v>
       </c>
       <c r="D43" t="s">
-        <v>803</v>
+        <v>740</v>
       </c>
       <c r="E43" t="s">
-        <v>815</v>
+        <v>741</v>
       </c>
       <c r="F43" t="s">
-        <v>816</v>
+        <v>742</v>
       </c>
       <c r="G43" t="s">
-        <v>817</v>
+        <v>743</v>
       </c>
       <c r="H43" t="s">
-        <v>818</v>
+        <v>744</v>
       </c>
       <c r="I43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J43" t="s">
         <v>19</v>
@@ -13788,10 +13845,10 @@
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="B44" t="s">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="C44" t="s">
         <v>45</v>
@@ -13800,16 +13857,16 @@
         <v>803</v>
       </c>
       <c r="E44" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="F44" t="s">
-        <v>805</v>
+        <v>816</v>
       </c>
       <c r="G44" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="H44" t="s">
-        <v>812</v>
+        <v>818</v>
       </c>
       <c r="I44" t="s">
         <v>19</v>
@@ -13820,10 +13877,10 @@
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="B45" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="C45" t="s">
         <v>45</v>
@@ -13832,16 +13889,16 @@
         <v>803</v>
       </c>
       <c r="E45" t="s">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="F45" t="s">
         <v>805</v>
       </c>
       <c r="G45" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="H45" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="I45" t="s">
         <v>19</v>
@@ -13852,28 +13909,28 @@
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>850</v>
+        <v>801</v>
       </c>
       <c r="B46" t="s">
-        <v>851</v>
+        <v>802</v>
       </c>
       <c r="C46" t="s">
         <v>45</v>
       </c>
       <c r="D46" t="s">
-        <v>845</v>
+        <v>803</v>
       </c>
       <c r="E46" t="s">
-        <v>846</v>
+        <v>804</v>
       </c>
       <c r="F46" t="s">
-        <v>852</v>
+        <v>805</v>
       </c>
       <c r="G46" t="s">
-        <v>853</v>
+        <v>806</v>
       </c>
       <c r="H46" t="s">
-        <v>854</v>
+        <v>807</v>
       </c>
       <c r="I46" t="s">
         <v>19</v>
@@ -13884,31 +13941,31 @@
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>844</v>
+        <v>853</v>
       </c>
       <c r="B47" t="s">
-        <v>44</v>
+        <v>854</v>
       </c>
       <c r="C47" t="s">
         <v>45</v>
       </c>
       <c r="D47" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="E47" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="F47" t="s">
-        <v>847</v>
+        <v>855</v>
       </c>
       <c r="G47" t="s">
-        <v>848</v>
+        <v>856</v>
       </c>
       <c r="H47" t="s">
-        <v>849</v>
+        <v>857</v>
       </c>
       <c r="I47" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J47" t="s">
         <v>19</v>
@@ -13916,31 +13973,31 @@
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>962</v>
+        <v>847</v>
       </c>
       <c r="B48" t="s">
-        <v>963</v>
+        <v>44</v>
       </c>
       <c r="C48" t="s">
         <v>45</v>
       </c>
       <c r="D48" t="s">
-        <v>953</v>
+        <v>848</v>
       </c>
       <c r="E48" t="s">
-        <v>954</v>
+        <v>849</v>
       </c>
       <c r="F48" t="s">
-        <v>955</v>
+        <v>850</v>
       </c>
       <c r="G48" t="s">
-        <v>964</v>
+        <v>851</v>
       </c>
       <c r="H48" t="s">
-        <v>965</v>
+        <v>852</v>
       </c>
       <c r="I48" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J48" t="s">
         <v>19</v>
@@ -13948,28 +14005,28 @@
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>958</v>
+        <v>965</v>
       </c>
       <c r="B49" t="s">
-        <v>959</v>
+        <v>966</v>
       </c>
       <c r="C49" t="s">
         <v>45</v>
       </c>
       <c r="D49" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="E49" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="F49" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="G49" t="s">
-        <v>960</v>
+        <v>967</v>
       </c>
       <c r="H49" t="s">
-        <v>961</v>
+        <v>968</v>
       </c>
       <c r="I49" t="s">
         <v>19</v>
@@ -13980,31 +14037,31 @@
     </row>
     <row r="50" spans="1:10">
       <c r="A50" t="s">
-        <v>951</v>
+        <v>961</v>
       </c>
       <c r="B50" t="s">
-        <v>952</v>
+        <v>962</v>
       </c>
       <c r="C50" t="s">
         <v>45</v>
       </c>
       <c r="D50" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="E50" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="F50" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="G50" t="s">
-        <v>956</v>
+        <v>963</v>
       </c>
       <c r="H50" t="s">
-        <v>957</v>
+        <v>964</v>
       </c>
       <c r="I50" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J50" t="s">
         <v>19</v>
@@ -14012,39 +14069,71 @@
     </row>
     <row r="51" spans="1:10">
       <c r="A51" t="s">
-        <v>988</v>
+        <v>954</v>
       </c>
       <c r="B51" t="s">
-        <v>466</v>
+        <v>955</v>
       </c>
       <c r="C51" t="s">
         <v>45</v>
       </c>
       <c r="D51" t="s">
-        <v>989</v>
+        <v>956</v>
       </c>
       <c r="E51" t="s">
-        <v>990</v>
+        <v>957</v>
       </c>
       <c r="F51" t="s">
+        <v>958</v>
+      </c>
+      <c r="G51" t="s">
+        <v>959</v>
+      </c>
+      <c r="H51" t="s">
+        <v>960</v>
+      </c>
+      <c r="I51" t="s">
+        <v>18</v>
+      </c>
+      <c r="J51" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" t="s">
         <v>991</v>
       </c>
-      <c r="G51" t="s">
+      <c r="B52" t="s">
+        <v>466</v>
+      </c>
+      <c r="C52" t="s">
+        <v>45</v>
+      </c>
+      <c r="D52" t="s">
         <v>992</v>
       </c>
-      <c r="H51" t="s">
+      <c r="E52" t="s">
         <v>993</v>
       </c>
-      <c r="I51" t="s">
-        <v>19</v>
-      </c>
-      <c r="J51" t="s">
+      <c r="F52" t="s">
+        <v>994</v>
+      </c>
+      <c r="G52" t="s">
+        <v>995</v>
+      </c>
+      <c r="H52" t="s">
+        <v>996</v>
+      </c>
+      <c r="I52" t="s">
+        <v>19</v>
+      </c>
+      <c r="J52" t="s">
         <v>19</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J51">
-    <sortCondition ref="D2:D51"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J52">
+    <sortCondition ref="D2:D52"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15348,28 +15437,28 @@
     </row>
     <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="B41" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="C41" t="s">
         <v>27</v>
       </c>
       <c r="D41" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="E41" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="F41" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="G41" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="H41" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="I41" t="s">
         <v>19</v>
@@ -15380,7 +15469,7 @@
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B42" t="s">
         <v>466</v>
@@ -15389,19 +15478,19 @@
         <v>27</v>
       </c>
       <c r="D42" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="E42" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="F42" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="G42" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="H42" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="I42" t="s">
         <v>19</v>
@@ -15412,28 +15501,28 @@
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="B43" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C43" t="s">
         <v>27</v>
       </c>
       <c r="D43" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="E43" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="F43" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="G43" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="H43" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="I43" t="s">
         <v>19</v>
@@ -15444,7 +15533,7 @@
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="B44" t="s">
         <v>466</v>
@@ -15453,19 +15542,19 @@
         <v>27</v>
       </c>
       <c r="D44" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="E44" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="F44" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="G44" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="H44" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="I44" t="s">
         <v>19</v>
@@ -15476,28 +15565,28 @@
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="B45" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C45" t="s">
         <v>27</v>
       </c>
       <c r="D45" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="E45" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="F45" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="G45" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="H45" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="I45" t="s">
         <v>19</v>
@@ -15508,28 +15597,28 @@
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="B46" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="C46" t="s">
         <v>27</v>
       </c>
       <c r="D46" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="E46" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="F46" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="G46" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="H46" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="I46" t="s">
         <v>19</v>
@@ -15540,28 +15629,28 @@
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="B47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C47" t="s">
         <v>27</v>
       </c>
       <c r="D47" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="E47" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="F47" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="G47" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="H47" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="I47" t="s">
         <v>19</v>
@@ -15572,28 +15661,28 @@
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="B48" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="C48" t="s">
         <v>27</v>
       </c>
       <c r="D48" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="E48" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="F48" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="G48" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="H48" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="I48" t="s">
         <v>18</v>
@@ -15604,28 +15693,28 @@
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B49" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="C49" t="s">
         <v>27</v>
       </c>
       <c r="D49" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="E49" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="F49" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="G49" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="H49" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="I49" t="s">
         <v>19</v>
@@ -15636,28 +15725,28 @@
     </row>
     <row r="50" spans="1:10" ht="30.75">
       <c r="A50" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="B50" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="C50" t="s">
         <v>27</v>
       </c>
       <c r="D50" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="F50" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="G50" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="H50" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="I50" t="s">
         <v>19</v>
@@ -15668,28 +15757,28 @@
     </row>
     <row r="51" spans="1:10">
       <c r="A51" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="B51" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="C51" t="s">
         <v>27</v>
       </c>
       <c r="D51" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="E51" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="F51" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="G51" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="H51" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="I51" t="s">
         <v>18</v>
@@ -15700,28 +15789,28 @@
     </row>
     <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="B52" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="C52" t="s">
         <v>27</v>
       </c>
       <c r="D52" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="E52" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="F52" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="G52" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="H52" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="I52" t="s">
         <v>18</v>
@@ -15732,7 +15821,7 @@
     </row>
     <row r="53" spans="1:10">
       <c r="A53" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="B53" t="s">
         <v>229</v>
@@ -15741,19 +15830,19 @@
         <v>27</v>
       </c>
       <c r="D53" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="E53" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="F53" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="G53" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="H53" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="I53" t="s">
         <v>19</v>
@@ -16026,7 +16115,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -16756,13 +16845,13 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>667</v>
+        <v>1007</v>
       </c>
       <c r="B34" t="s">
         <v>134</v>
       </c>
       <c r="C34" t="s">
-        <v>672</v>
+        <v>1008</v>
       </c>
       <c r="D34" t="s">
         <v>45</v>
@@ -16825,19 +16914,19 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="B37" t="s">
         <v>134</v>
       </c>
       <c r="C37" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="D37" t="s">
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="F37" t="s">
         <v>18</v>
@@ -16848,19 +16937,19 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="B38" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="C38" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="D38" t="s">
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="F38" t="s">
         <v>18</v>
@@ -16871,19 +16960,19 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="B39" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="C39" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="D39" t="s">
         <v>45</v>
       </c>
       <c r="E39" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="F39" t="s">
         <v>18</v>
@@ -16894,19 +16983,19 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="B40" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="C40" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="D40" t="s">
         <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="F40" t="s">
         <v>18</v>
@@ -16963,19 +17052,19 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="B43" t="s">
-        <v>827</v>
+        <v>998</v>
       </c>
       <c r="C43" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="D43" t="s">
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="F43" t="s">
         <v>18</v>
@@ -16986,19 +17075,19 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="B44" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="C44" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="D44" t="s">
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="F44" t="s">
         <v>18</v>
@@ -17009,19 +17098,19 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="B45" t="s">
         <v>44</v>
       </c>
       <c r="C45" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="D45" t="s">
         <v>45</v>
       </c>
       <c r="E45" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="F45" t="s">
         <v>18</v>
@@ -17032,19 +17121,19 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="B46" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="C46" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="D46" t="s">
         <v>27</v>
       </c>
       <c r="E46" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="F46" t="s">
         <v>18</v>
@@ -17055,19 +17144,19 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="B47" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="C47" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="D47" t="s">
         <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="F47" t="s">
         <v>18</v>
@@ -17078,19 +17167,19 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B48" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="C48" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="D48" t="s">
         <v>45</v>
       </c>
       <c r="E48" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="F48" t="s">
         <v>18</v>
@@ -17101,19 +17190,19 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="B49" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="C49" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="D49" t="s">
         <v>27</v>
       </c>
       <c r="E49" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="F49" t="s">
         <v>18</v>
@@ -17124,19 +17213,19 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="B50" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="C50" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="D50" t="s">
         <v>27</v>
       </c>
       <c r="E50" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="F50" t="s">
         <v>18</v>
@@ -17154,30 +17243,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="16f6d35e-f8f7-4be7-8a36-77a5301d0496">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="995fa42e-70f2-45ca-a92e-66b9e5c12198" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004B288D62A9D4EB43B1B4847ADFD34D72" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e2552ced7a26529371015a9423690663">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="16f6d35e-f8f7-4be7-8a36-77a5301d0496" xmlns:ns3="995fa42e-70f2-45ca-a92e-66b9e5c12198" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c694927967977ecf129d2b495a882391" ns2:_="" ns3:_="">
-    <xsd:import namespace="16f6d35e-f8f7-4be7-8a36-77a5301d0496"/>
-    <xsd:import namespace="995fa42e-70f2-45ca-a92e-66b9e5c12198"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004D2A734076944F4C8CF2F92970507CB2" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9c0425cef60a2b3ac47217493dc3205f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30aff7f6-e59e-4da9-89fc-ab8594e23593" xmlns:ns3="4e599274-3222-4cb5-ba5a-ff9704aa99fe" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d2991b6fe5944e93c9f57f4005d80324" ns2:_="" ns3:_="">
+    <xsd:import namespace="30aff7f6-e59e-4da9-89fc-ab8594e23593"/>
+    <xsd:import namespace="4e599274-3222-4cb5-ba5a-ff9704aa99fe"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -17186,19 +17255,16 @@
               <xsd:all>
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
@@ -17208,7 +17274,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="16f6d35e-f8f7-4be7-8a36-77a5301d0496" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="30aff7f6-e59e-4da9-89fc-ab8594e23593" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -17221,41 +17287,41 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="10" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="11" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+    <xsd:element name="MediaLengthInSeconds" ma:index="13" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="14" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="15" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="16" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
     <xsd:element name="MediaServiceOCR" ma:index="17" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
@@ -17265,59 +17331,28 @@
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="e2634a7c-d88b-4a2c-8388-1a3d08c06d4e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="dd127b8f-fb8f-4d4b-acb8-087e4b00ae48" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
         </xsd:sequence>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="21" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="995fa42e-70f2-45ca-a92e-66b9e5c12198" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="4e599274-3222-4cb5-ba5a-ff9704aa99fe" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{814c3b3f-5ace-4537-970c-a2f2119d6d26}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="995fa42e-70f2-45ca-a92e-66b9e5c12198">
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{45b9ee37-3475-4ddb-8fa8-f1166d9d8ad1}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="4e599274-3222-4cb5-ba5a-ff9704aa99fe">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:MultiChoiceLookup">
@@ -17428,8 +17463,28 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="30aff7f6-e59e-4da9-89fc-ab8594e23593">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4e599274-3222-4cb5-ba5a-ff9704aa99fe" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D62CAFA9-65B1-461F-9362-F8CA4127393E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D23443B-4957-4117-93FE-EC14E7669A03}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17437,5 +17492,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2ED8D836-5E5B-4503-84E9-B63382437957}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D62CAFA9-65B1-461F-9362-F8CA4127393E}"/>
 </file>